--- a/Investment Tracking V3.xlsx
+++ b/Investment Tracking V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acmfirm-my.sharepoint.com/personal/isaac_asselstine_treewalk_com/Documents/Documents/Investment Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4725" documentId="8_{B2161804-0EDF-42E0-BE0F-33C496CCEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A75F899D-302A-472B-95B8-8B9D15ED9FB7}"/>
+  <xr:revisionPtr revIDLastSave="4733" documentId="8_{B2161804-0EDF-42E0-BE0F-33C496CCEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7286CD7D-4D8F-4066-8596-CBD419379FF2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D310D58-D25C-478B-96CD-BDDADD687EF5}"/>
   </bookViews>
@@ -472,13 +472,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -839,40 +839,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:28" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="H2" s="45" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="H2" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
       <c r="L2" s="39"/>
       <c r="M2" s="39" t="s">
         <v>44</v>
       </c>
       <c r="N2" s="39"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="45" t="s">
+      <c r="P2" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="46" t="s">
+      <c r="X2" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
     </row>
     <row r="3" spans="3:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C3" s="15" t="s">
@@ -973,10 +973,19 @@
       <c r="X4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="44"/>
+      <c r="Y4" s="44">
+        <f>SUM(U4:U252)</f>
+        <v>0</v>
+      </c>
       <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
+      <c r="AA4" s="44">
+        <f>Y4-Z4</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="44" t="str">
+        <f>IF(AA4=0,"✓","!")</f>
+        <v>✓</v>
+      </c>
     </row>
     <row r="5" spans="3:28" x14ac:dyDescent="0.25">
       <c r="L5" s="17" cm="1">
@@ -1011,10 +1020,19 @@
       <c r="X5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Y5" s="44"/>
+      <c r="Y5" s="44">
+        <f>Y4</f>
+        <v>0</v>
+      </c>
       <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
+      <c r="AA5" s="44">
+        <f>Y5-Z5</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="44" t="str">
+        <f t="shared" ref="AB5:AB6" si="3">IF(AA5=0,"✓","!")</f>
+        <v>✓</v>
+      </c>
     </row>
     <row r="6" spans="3:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L6" s="17" cm="1">
@@ -1049,10 +1067,22 @@
       <c r="X6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
+      <c r="Y6" s="45">
+        <f>Y5+Y4</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="45">
+        <f t="shared" ref="Z6:AB6" si="4">Z5+Z4</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="45" t="str">
+        <f t="shared" si="3"/>
+        <v>✓</v>
+      </c>
     </row>
     <row r="7" spans="3:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="L7" s="17" cm="1">
@@ -2990,15 +3020,15 @@
         <v>0</v>
       </c>
       <c r="P69" s="17">
-        <f t="shared" ref="P69:P132" si="3">H69+M69</f>
+        <f t="shared" ref="P69:P132" si="5">H69+M69</f>
         <v>0</v>
       </c>
       <c r="Q69" s="17">
-        <f t="shared" ref="Q69:Q132" si="4">I69+L69</f>
+        <f t="shared" ref="Q69:Q132" si="6">I69+L69</f>
         <v>0</v>
       </c>
       <c r="R69" t="str">
-        <f t="shared" ref="R69:R132" si="5">IFERROR(P69/Q69, "")</f>
+        <f t="shared" ref="R69:R132" si="7">IFERROR(P69/Q69, "")</f>
         <v/>
       </c>
       <c r="S69" s="26" t="str" cm="1">
@@ -3021,15 +3051,15 @@
         <v>0</v>
       </c>
       <c r="P70" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q70" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R70" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S70" s="26" t="str" cm="1">
@@ -3052,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="P71" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q71" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S71" s="26" t="str" cm="1">
@@ -3083,15 +3113,15 @@
         <v>0</v>
       </c>
       <c r="P72" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q72" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R72" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S72" s="26" t="str" cm="1">
@@ -3114,15 +3144,15 @@
         <v>0</v>
       </c>
       <c r="P73" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q73" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R73" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S73" s="26" t="str" cm="1">
@@ -3145,15 +3175,15 @@
         <v>0</v>
       </c>
       <c r="P74" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q74" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S74" s="26" t="str" cm="1">
@@ -3176,15 +3206,15 @@
         <v>0</v>
       </c>
       <c r="P75" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q75" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R75" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S75" s="26" t="str" cm="1">
@@ -3207,15 +3237,15 @@
         <v>0</v>
       </c>
       <c r="P76" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q76" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R76" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S76" s="26" t="str" cm="1">
@@ -3238,15 +3268,15 @@
         <v>0</v>
       </c>
       <c r="P77" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q77" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S77" s="26" t="str" cm="1">
@@ -3269,15 +3299,15 @@
         <v>0</v>
       </c>
       <c r="P78" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q78" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S78" s="26" t="str" cm="1">
@@ -3300,15 +3330,15 @@
         <v>0</v>
       </c>
       <c r="P79" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R79" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S79" s="26" t="str" cm="1">
@@ -3331,15 +3361,15 @@
         <v>0</v>
       </c>
       <c r="P80" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q80" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S80" s="26" t="str" cm="1">
@@ -3362,15 +3392,15 @@
         <v>0</v>
       </c>
       <c r="P81" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q81" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S81" s="26" t="str" cm="1">
@@ -3393,15 +3423,15 @@
         <v>0</v>
       </c>
       <c r="P82" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q82" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R82" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S82" s="26" t="str" cm="1">
@@ -3424,15 +3454,15 @@
         <v>0</v>
       </c>
       <c r="P83" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q83" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R83" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S83" s="26" t="str" cm="1">
@@ -3455,15 +3485,15 @@
         <v>0</v>
       </c>
       <c r="P84" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q84" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S84" s="26" t="str" cm="1">
@@ -3486,15 +3516,15 @@
         <v>0</v>
       </c>
       <c r="P85" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q85" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R85" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S85" s="26" t="str" cm="1">
@@ -3517,15 +3547,15 @@
         <v>0</v>
       </c>
       <c r="P86" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q86" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S86" s="26" t="str" cm="1">
@@ -3548,15 +3578,15 @@
         <v>0</v>
       </c>
       <c r="P87" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q87" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S87" s="26" t="str" cm="1">
@@ -3579,15 +3609,15 @@
         <v>0</v>
       </c>
       <c r="P88" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q88" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S88" s="26" t="str" cm="1">
@@ -3610,15 +3640,15 @@
         <v>0</v>
       </c>
       <c r="P89" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q89" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S89" s="26" t="str" cm="1">
@@ -3641,15 +3671,15 @@
         <v>0</v>
       </c>
       <c r="P90" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q90" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R90" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S90" s="26" t="str" cm="1">
@@ -3672,15 +3702,15 @@
         <v>0</v>
       </c>
       <c r="P91" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q91" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R91" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S91" s="26" t="str" cm="1">
@@ -3703,15 +3733,15 @@
         <v>0</v>
       </c>
       <c r="P92" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q92" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R92" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S92" s="26" t="str" cm="1">
@@ -3734,15 +3764,15 @@
         <v>0</v>
       </c>
       <c r="P93" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q93" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R93" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S93" s="26" t="str" cm="1">
@@ -3765,15 +3795,15 @@
         <v>0</v>
       </c>
       <c r="P94" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q94" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R94" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S94" s="26" t="str" cm="1">
@@ -3796,15 +3826,15 @@
         <v>0</v>
       </c>
       <c r="P95" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q95" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R95" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S95" s="26" t="str" cm="1">
@@ -3827,15 +3857,15 @@
         <v>0</v>
       </c>
       <c r="P96" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q96" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R96" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S96" s="26" t="str" cm="1">
@@ -3858,15 +3888,15 @@
         <v>0</v>
       </c>
       <c r="P97" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q97" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R97" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S97" s="26" t="str" cm="1">
@@ -3889,15 +3919,15 @@
         <v>0</v>
       </c>
       <c r="P98" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q98" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R98" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S98" s="26" t="str" cm="1">
@@ -3920,15 +3950,15 @@
         <v>0</v>
       </c>
       <c r="P99" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q99" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R99" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S99" s="26" t="str" cm="1">
@@ -3951,15 +3981,15 @@
         <v>0</v>
       </c>
       <c r="P100" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q100" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R100" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S100" s="26" t="str" cm="1">
@@ -3982,15 +4012,15 @@
         <v>0</v>
       </c>
       <c r="P101" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q101" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R101" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S101" s="26" t="str" cm="1">
@@ -4013,15 +4043,15 @@
         <v>0</v>
       </c>
       <c r="P102" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q102" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R102" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S102" s="26" t="str" cm="1">
@@ -4044,15 +4074,15 @@
         <v>0</v>
       </c>
       <c r="P103" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q103" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R103" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S103" s="26" t="str" cm="1">
@@ -4075,15 +4105,15 @@
         <v>0</v>
       </c>
       <c r="P104" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q104" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R104" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S104" s="26" t="str" cm="1">
@@ -4106,15 +4136,15 @@
         <v>0</v>
       </c>
       <c r="P105" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q105" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R105" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S105" s="26" t="str" cm="1">
@@ -4137,15 +4167,15 @@
         <v>0</v>
       </c>
       <c r="P106" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q106" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R106" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S106" s="26" t="str" cm="1">
@@ -4168,15 +4198,15 @@
         <v>0</v>
       </c>
       <c r="P107" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q107" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R107" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S107" s="26" t="str" cm="1">
@@ -4199,15 +4229,15 @@
         <v>0</v>
       </c>
       <c r="P108" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q108" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R108" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S108" s="26" t="str" cm="1">
@@ -4230,15 +4260,15 @@
         <v>0</v>
       </c>
       <c r="P109" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q109" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R109" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S109" s="26" t="str" cm="1">
@@ -4261,15 +4291,15 @@
         <v>0</v>
       </c>
       <c r="P110" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q110" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R110" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S110" s="26" t="str" cm="1">
@@ -4292,15 +4322,15 @@
         <v>0</v>
       </c>
       <c r="P111" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q111" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R111" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S111" s="26" t="str" cm="1">
@@ -4323,15 +4353,15 @@
         <v>0</v>
       </c>
       <c r="P112" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q112" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R112" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S112" s="26" t="str" cm="1">
@@ -4354,15 +4384,15 @@
         <v>0</v>
       </c>
       <c r="P113" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q113" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R113" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S113" s="26" t="str" cm="1">
@@ -4385,15 +4415,15 @@
         <v>0</v>
       </c>
       <c r="P114" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q114" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R114" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S114" s="26" t="str" cm="1">
@@ -4416,15 +4446,15 @@
         <v>0</v>
       </c>
       <c r="P115" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q115" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R115" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S115" s="26" t="str" cm="1">
@@ -4447,15 +4477,15 @@
         <v>0</v>
       </c>
       <c r="P116" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q116" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R116" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S116" s="26" t="str" cm="1">
@@ -4478,15 +4508,15 @@
         <v>0</v>
       </c>
       <c r="P117" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q117" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R117" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S117" s="26" t="str" cm="1">
@@ -4509,15 +4539,15 @@
         <v>0</v>
       </c>
       <c r="P118" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q118" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R118" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S118" s="26" t="str" cm="1">
@@ -4540,15 +4570,15 @@
         <v>0</v>
       </c>
       <c r="P119" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q119" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R119" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S119" s="26" t="str" cm="1">
@@ -4571,15 +4601,15 @@
         <v>0</v>
       </c>
       <c r="P120" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q120" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R120" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S120" s="26" t="str" cm="1">
@@ -4602,15 +4632,15 @@
         <v>0</v>
       </c>
       <c r="P121" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q121" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R121" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S121" s="26" t="str" cm="1">
@@ -4633,15 +4663,15 @@
         <v>0</v>
       </c>
       <c r="P122" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q122" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S122" s="26" t="str" cm="1">
@@ -4664,15 +4694,15 @@
         <v>0</v>
       </c>
       <c r="P123" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q123" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R123" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S123" s="26" t="str" cm="1">
@@ -4695,15 +4725,15 @@
         <v>0</v>
       </c>
       <c r="P124" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q124" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R124" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S124" s="26" t="str" cm="1">
@@ -4726,15 +4756,15 @@
         <v>0</v>
       </c>
       <c r="P125" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q125" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R125" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S125" s="26" t="str" cm="1">
@@ -4757,15 +4787,15 @@
         <v>0</v>
       </c>
       <c r="P126" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q126" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S126" s="26" t="str" cm="1">
@@ -4788,15 +4818,15 @@
         <v>0</v>
       </c>
       <c r="P127" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q127" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R127" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S127" s="26" t="str" cm="1">
@@ -4819,15 +4849,15 @@
         <v>0</v>
       </c>
       <c r="P128" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q128" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R128" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S128" s="26" t="str" cm="1">
@@ -4850,15 +4880,15 @@
         <v>0</v>
       </c>
       <c r="P129" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q129" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R129" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S129" s="26" t="str" cm="1">
@@ -4881,15 +4911,15 @@
         <v>0</v>
       </c>
       <c r="P130" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q130" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R130" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S130" s="26" t="str" cm="1">
@@ -4912,15 +4942,15 @@
         <v>0</v>
       </c>
       <c r="P131" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q131" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R131" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S131" s="26" t="str" cm="1">
@@ -4943,15 +4973,15 @@
         <v>0</v>
       </c>
       <c r="P132" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q132" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R132" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="S132" s="26" t="str" cm="1">
@@ -4974,15 +5004,15 @@
         <v>0</v>
       </c>
       <c r="P133" s="17">
-        <f t="shared" ref="P133:P196" si="6">H133+M133</f>
+        <f t="shared" ref="P133:P196" si="8">H133+M133</f>
         <v>0</v>
       </c>
       <c r="Q133" s="17">
-        <f t="shared" ref="Q133:Q196" si="7">I133+L133</f>
+        <f t="shared" ref="Q133:Q196" si="9">I133+L133</f>
         <v>0</v>
       </c>
       <c r="R133" t="str">
-        <f t="shared" ref="R133:R196" si="8">IFERROR(P133/Q133, "")</f>
+        <f t="shared" ref="R133:R196" si="10">IFERROR(P133/Q133, "")</f>
         <v/>
       </c>
       <c r="S133" s="26" t="str" cm="1">
@@ -5005,15 +5035,15 @@
         <v>0</v>
       </c>
       <c r="P134" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q134" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R134" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S134" s="26" t="str" cm="1">
@@ -5036,15 +5066,15 @@
         <v>0</v>
       </c>
       <c r="P135" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q135" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R135" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S135" s="26" t="str" cm="1">
@@ -5067,15 +5097,15 @@
         <v>0</v>
       </c>
       <c r="P136" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q136" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S136" s="26" t="str" cm="1">
@@ -5098,15 +5128,15 @@
         <v>0</v>
       </c>
       <c r="P137" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q137" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R137" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S137" s="26" t="str" cm="1">
@@ -5129,15 +5159,15 @@
         <v>0</v>
       </c>
       <c r="P138" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q138" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R138" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S138" s="26" t="str" cm="1">
@@ -5160,15 +5190,15 @@
         <v>0</v>
       </c>
       <c r="P139" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q139" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R139" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S139" s="26" t="str" cm="1">
@@ -5191,15 +5221,15 @@
         <v>0</v>
       </c>
       <c r="P140" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q140" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R140" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S140" s="26" t="str" cm="1">
@@ -5222,15 +5252,15 @@
         <v>0</v>
       </c>
       <c r="P141" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q141" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R141" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S141" s="26" t="str" cm="1">
@@ -5253,15 +5283,15 @@
         <v>0</v>
       </c>
       <c r="P142" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q142" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R142" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S142" s="26" t="str" cm="1">
@@ -5284,15 +5314,15 @@
         <v>0</v>
       </c>
       <c r="P143" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q143" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R143" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S143" s="26" t="str" cm="1">
@@ -5315,15 +5345,15 @@
         <v>0</v>
       </c>
       <c r="P144" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q144" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R144" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S144" s="26" t="str" cm="1">
@@ -5346,15 +5376,15 @@
         <v>0</v>
       </c>
       <c r="P145" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q145" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R145" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S145" s="26" t="str" cm="1">
@@ -5377,15 +5407,15 @@
         <v>0</v>
       </c>
       <c r="P146" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q146" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R146" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S146" s="26" t="str" cm="1">
@@ -5408,15 +5438,15 @@
         <v>0</v>
       </c>
       <c r="P147" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q147" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R147" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S147" s="26" t="str" cm="1">
@@ -5439,15 +5469,15 @@
         <v>0</v>
       </c>
       <c r="P148" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q148" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R148" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S148" s="26" t="str" cm="1">
@@ -5470,15 +5500,15 @@
         <v>0</v>
       </c>
       <c r="P149" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q149" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R149" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S149" s="26" t="str" cm="1">
@@ -5501,15 +5531,15 @@
         <v>0</v>
       </c>
       <c r="P150" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q150" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R150" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S150" s="26" t="str" cm="1">
@@ -5532,15 +5562,15 @@
         <v>0</v>
       </c>
       <c r="P151" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q151" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R151" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S151" s="26" t="str" cm="1">
@@ -5563,15 +5593,15 @@
         <v>0</v>
       </c>
       <c r="P152" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q152" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R152" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S152" s="26" t="str" cm="1">
@@ -5594,15 +5624,15 @@
         <v>0</v>
       </c>
       <c r="P153" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q153" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R153" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S153" s="26" t="str" cm="1">
@@ -5625,15 +5655,15 @@
         <v>0</v>
       </c>
       <c r="P154" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q154" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R154" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S154" s="26" t="str" cm="1">
@@ -5656,15 +5686,15 @@
         <v>0</v>
       </c>
       <c r="P155" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q155" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R155" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S155" s="26" t="str" cm="1">
@@ -5687,15 +5717,15 @@
         <v>0</v>
       </c>
       <c r="P156" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q156" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R156" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S156" s="26" t="str" cm="1">
@@ -5718,15 +5748,15 @@
         <v>0</v>
       </c>
       <c r="P157" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q157" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R157" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S157" s="26" t="str" cm="1">
@@ -5749,15 +5779,15 @@
         <v>0</v>
       </c>
       <c r="P158" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q158" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R158" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S158" s="26" t="str" cm="1">
@@ -5780,15 +5810,15 @@
         <v>0</v>
       </c>
       <c r="P159" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q159" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R159" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S159" s="26" t="str" cm="1">
@@ -5811,15 +5841,15 @@
         <v>0</v>
       </c>
       <c r="P160" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q160" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R160" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S160" s="26" t="str" cm="1">
@@ -5842,15 +5872,15 @@
         <v>0</v>
       </c>
       <c r="P161" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q161" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R161" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S161" s="26" t="str" cm="1">
@@ -5873,15 +5903,15 @@
         <v>0</v>
       </c>
       <c r="P162" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q162" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R162" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S162" s="26" t="str" cm="1">
@@ -5904,15 +5934,15 @@
         <v>0</v>
       </c>
       <c r="P163" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q163" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R163" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S163" s="26" t="str" cm="1">
@@ -5935,15 +5965,15 @@
         <v>0</v>
       </c>
       <c r="P164" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q164" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R164" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S164" s="26" t="str" cm="1">
@@ -5966,15 +5996,15 @@
         <v>0</v>
       </c>
       <c r="P165" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q165" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R165" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S165" s="26" t="str" cm="1">
@@ -5997,15 +6027,15 @@
         <v>0</v>
       </c>
       <c r="P166" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q166" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R166" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S166" s="26" t="str" cm="1">
@@ -6028,15 +6058,15 @@
         <v>0</v>
       </c>
       <c r="P167" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q167" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R167" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S167" s="26" t="str" cm="1">
@@ -6059,15 +6089,15 @@
         <v>0</v>
       </c>
       <c r="P168" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q168" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R168" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S168" s="26" t="str" cm="1">
@@ -6090,15 +6120,15 @@
         <v>0</v>
       </c>
       <c r="P169" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q169" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R169" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S169" s="26" t="str" cm="1">
@@ -6121,15 +6151,15 @@
         <v>0</v>
       </c>
       <c r="P170" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q170" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R170" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S170" s="26" t="str" cm="1">
@@ -6152,15 +6182,15 @@
         <v>0</v>
       </c>
       <c r="P171" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q171" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R171" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S171" s="26" t="str" cm="1">
@@ -6183,15 +6213,15 @@
         <v>0</v>
       </c>
       <c r="P172" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q172" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R172" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S172" s="26" t="str" cm="1">
@@ -6214,15 +6244,15 @@
         <v>0</v>
       </c>
       <c r="P173" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q173" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R173" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S173" s="26" t="str" cm="1">
@@ -6245,15 +6275,15 @@
         <v>0</v>
       </c>
       <c r="P174" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q174" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R174" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S174" s="26" t="str" cm="1">
@@ -6276,15 +6306,15 @@
         <v>0</v>
       </c>
       <c r="P175" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q175" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R175" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S175" s="26" t="str" cm="1">
@@ -6307,15 +6337,15 @@
         <v>0</v>
       </c>
       <c r="P176" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q176" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R176" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S176" s="26" t="str" cm="1">
@@ -6338,15 +6368,15 @@
         <v>0</v>
       </c>
       <c r="P177" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q177" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R177" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S177" s="26" t="str" cm="1">
@@ -6369,15 +6399,15 @@
         <v>0</v>
       </c>
       <c r="P178" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q178" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R178" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S178" s="26" t="str" cm="1">
@@ -6400,15 +6430,15 @@
         <v>0</v>
       </c>
       <c r="P179" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q179" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R179" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S179" s="26" t="str" cm="1">
@@ -6431,15 +6461,15 @@
         <v>0</v>
       </c>
       <c r="P180" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q180" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R180" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S180" s="26" t="str" cm="1">
@@ -6462,15 +6492,15 @@
         <v>0</v>
       </c>
       <c r="P181" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q181" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R181" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S181" s="26" t="str" cm="1">
@@ -6493,15 +6523,15 @@
         <v>0</v>
       </c>
       <c r="P182" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q182" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R182" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S182" s="26" t="str" cm="1">
@@ -6524,15 +6554,15 @@
         <v>0</v>
       </c>
       <c r="P183" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q183" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R183" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S183" s="26" t="str" cm="1">
@@ -6555,15 +6585,15 @@
         <v>0</v>
       </c>
       <c r="P184" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q184" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R184" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S184" s="26" t="str" cm="1">
@@ -6586,15 +6616,15 @@
         <v>0</v>
       </c>
       <c r="P185" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q185" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R185" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S185" s="26" t="str" cm="1">
@@ -6617,15 +6647,15 @@
         <v>0</v>
       </c>
       <c r="P186" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q186" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R186" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S186" s="26" t="str" cm="1">
@@ -6648,15 +6678,15 @@
         <v>0</v>
       </c>
       <c r="P187" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q187" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R187" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S187" s="26" t="str" cm="1">
@@ -6679,15 +6709,15 @@
         <v>0</v>
       </c>
       <c r="P188" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q188" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R188" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S188" s="26" t="str" cm="1">
@@ -6710,15 +6740,15 @@
         <v>0</v>
       </c>
       <c r="P189" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q189" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R189" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S189" s="26" t="str" cm="1">
@@ -6741,15 +6771,15 @@
         <v>0</v>
       </c>
       <c r="P190" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q190" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R190" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S190" s="26" t="str" cm="1">
@@ -6772,15 +6802,15 @@
         <v>0</v>
       </c>
       <c r="P191" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q191" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R191" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S191" s="26" t="str" cm="1">
@@ -6803,15 +6833,15 @@
         <v>0</v>
       </c>
       <c r="P192" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q192" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R192" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S192" s="26" t="str" cm="1">
@@ -6834,15 +6864,15 @@
         <v>0</v>
       </c>
       <c r="P193" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q193" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R193" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S193" s="26" t="str" cm="1">
@@ -6865,15 +6895,15 @@
         <v>0</v>
       </c>
       <c r="P194" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q194" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R194" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S194" s="26" t="str" cm="1">
@@ -6896,15 +6926,15 @@
         <v>0</v>
       </c>
       <c r="P195" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q195" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R195" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S195" s="26" t="str" cm="1">
@@ -6927,15 +6957,15 @@
         <v>0</v>
       </c>
       <c r="P196" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q196" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R196" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S196" s="26" t="str" cm="1">
@@ -6958,15 +6988,15 @@
         <v>0</v>
       </c>
       <c r="P197" s="17">
-        <f t="shared" ref="P197:P252" si="9">H197+M197</f>
+        <f t="shared" ref="P197:P252" si="11">H197+M197</f>
         <v>0</v>
       </c>
       <c r="Q197" s="17">
-        <f t="shared" ref="Q197:Q252" si="10">I197+L197</f>
+        <f t="shared" ref="Q197:Q252" si="12">I197+L197</f>
         <v>0</v>
       </c>
       <c r="R197" t="str">
-        <f t="shared" ref="R197:R252" si="11">IFERROR(P197/Q197, "")</f>
+        <f t="shared" ref="R197:R252" si="13">IFERROR(P197/Q197, "")</f>
         <v/>
       </c>
       <c r="S197" s="26" t="str" cm="1">
@@ -6989,15 +7019,15 @@
         <v>0</v>
       </c>
       <c r="P198" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q198" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R198" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S198" s="26" t="str" cm="1">
@@ -7020,15 +7050,15 @@
         <v>0</v>
       </c>
       <c r="P199" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q199" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R199" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S199" s="26" t="str" cm="1">
@@ -7051,15 +7081,15 @@
         <v>0</v>
       </c>
       <c r="P200" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q200" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R200" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S200" s="26" t="str" cm="1">
@@ -7082,15 +7112,15 @@
         <v>0</v>
       </c>
       <c r="P201" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q201" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R201" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S201" s="26" t="str" cm="1">
@@ -7113,15 +7143,15 @@
         <v>0</v>
       </c>
       <c r="P202" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q202" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R202" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S202" s="26" t="str" cm="1">
@@ -7144,15 +7174,15 @@
         <v>0</v>
       </c>
       <c r="P203" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q203" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R203" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S203" s="26" t="str" cm="1">
@@ -7175,15 +7205,15 @@
         <v>0</v>
       </c>
       <c r="P204" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q204" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R204" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S204" s="26" t="str" cm="1">
@@ -7206,15 +7236,15 @@
         <v>0</v>
       </c>
       <c r="P205" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q205" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R205" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S205" s="26" t="str" cm="1">
@@ -7237,15 +7267,15 @@
         <v>0</v>
       </c>
       <c r="P206" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q206" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R206" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S206" s="26" t="str" cm="1">
@@ -7268,15 +7298,15 @@
         <v>0</v>
       </c>
       <c r="P207" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q207" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R207" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S207" s="26" t="str" cm="1">
@@ -7299,15 +7329,15 @@
         <v>0</v>
       </c>
       <c r="P208" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q208" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R208" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S208" s="26" t="str" cm="1">
@@ -7330,15 +7360,15 @@
         <v>0</v>
       </c>
       <c r="P209" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q209" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R209" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S209" s="26" t="str" cm="1">
@@ -7361,15 +7391,15 @@
         <v>0</v>
       </c>
       <c r="P210" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q210" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R210" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S210" s="26" t="str" cm="1">
@@ -7392,15 +7422,15 @@
         <v>0</v>
       </c>
       <c r="P211" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q211" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R211" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S211" s="26" t="str" cm="1">
@@ -7423,15 +7453,15 @@
         <v>0</v>
       </c>
       <c r="P212" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q212" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R212" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S212" s="26" t="str" cm="1">
@@ -7454,15 +7484,15 @@
         <v>0</v>
       </c>
       <c r="P213" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q213" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R213" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S213" s="26" t="str" cm="1">
@@ -7485,15 +7515,15 @@
         <v>0</v>
       </c>
       <c r="P214" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q214" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R214" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S214" s="26" t="str" cm="1">
@@ -7516,15 +7546,15 @@
         <v>0</v>
       </c>
       <c r="P215" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q215" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R215" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S215" s="26" t="str" cm="1">
@@ -7547,15 +7577,15 @@
         <v>0</v>
       </c>
       <c r="P216" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q216" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R216" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S216" s="26" t="str" cm="1">
@@ -7578,15 +7608,15 @@
         <v>0</v>
       </c>
       <c r="P217" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q217" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R217" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S217" s="26" t="str" cm="1">
@@ -7609,15 +7639,15 @@
         <v>0</v>
       </c>
       <c r="P218" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q218" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R218" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S218" s="26" t="str" cm="1">
@@ -7640,15 +7670,15 @@
         <v>0</v>
       </c>
       <c r="P219" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q219" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R219" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S219" s="26" t="str" cm="1">
@@ -7671,15 +7701,15 @@
         <v>0</v>
       </c>
       <c r="P220" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q220" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R220" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S220" s="26" t="str" cm="1">
@@ -7702,15 +7732,15 @@
         <v>0</v>
       </c>
       <c r="P221" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q221" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R221" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S221" s="26" t="str" cm="1">
@@ -7733,15 +7763,15 @@
         <v>0</v>
       </c>
       <c r="P222" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q222" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R222" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S222" s="26" t="str" cm="1">
@@ -7764,15 +7794,15 @@
         <v>0</v>
       </c>
       <c r="P223" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q223" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R223" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S223" s="26" t="str" cm="1">
@@ -7795,15 +7825,15 @@
         <v>0</v>
       </c>
       <c r="P224" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q224" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R224" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S224" s="26" t="str" cm="1">
@@ -7826,15 +7856,15 @@
         <v>0</v>
       </c>
       <c r="P225" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q225" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R225" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S225" s="26" t="str" cm="1">
@@ -7857,15 +7887,15 @@
         <v>0</v>
       </c>
       <c r="P226" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q226" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R226" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S226" s="26" t="str" cm="1">
@@ -7888,15 +7918,15 @@
         <v>0</v>
       </c>
       <c r="P227" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q227" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R227" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S227" s="26" t="str" cm="1">
@@ -7919,15 +7949,15 @@
         <v>0</v>
       </c>
       <c r="P228" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q228" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R228" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S228" s="26" t="str" cm="1">
@@ -7950,15 +7980,15 @@
         <v>0</v>
       </c>
       <c r="P229" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q229" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R229" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S229" s="26" t="str" cm="1">
@@ -7981,15 +8011,15 @@
         <v>0</v>
       </c>
       <c r="P230" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q230" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R230" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S230" s="26" t="str" cm="1">
@@ -8012,15 +8042,15 @@
         <v>0</v>
       </c>
       <c r="P231" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q231" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R231" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S231" s="26" t="str" cm="1">
@@ -8043,15 +8073,15 @@
         <v>0</v>
       </c>
       <c r="P232" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q232" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R232" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S232" s="26" t="str" cm="1">
@@ -8074,15 +8104,15 @@
         <v>0</v>
       </c>
       <c r="P233" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q233" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R233" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S233" s="26" t="str" cm="1">
@@ -8105,15 +8135,15 @@
         <v>0</v>
       </c>
       <c r="P234" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q234" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R234" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S234" s="26" t="str" cm="1">
@@ -8136,15 +8166,15 @@
         <v>0</v>
       </c>
       <c r="P235" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q235" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R235" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S235" s="26" t="str" cm="1">
@@ -8167,15 +8197,15 @@
         <v>0</v>
       </c>
       <c r="P236" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q236" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R236" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S236" s="26" t="str" cm="1">
@@ -8198,15 +8228,15 @@
         <v>0</v>
       </c>
       <c r="P237" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q237" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R237" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S237" s="26" t="str" cm="1">
@@ -8229,15 +8259,15 @@
         <v>0</v>
       </c>
       <c r="P238" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q238" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R238" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S238" s="26" t="str" cm="1">
@@ -8260,15 +8290,15 @@
         <v>0</v>
       </c>
       <c r="P239" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q239" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R239" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S239" s="26" t="str" cm="1">
@@ -8291,15 +8321,15 @@
         <v>0</v>
       </c>
       <c r="P240" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q240" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R240" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S240" s="26" t="str" cm="1">
@@ -8322,15 +8352,15 @@
         <v>0</v>
       </c>
       <c r="P241" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q241" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R241" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S241" s="26" t="str" cm="1">
@@ -8353,15 +8383,15 @@
         <v>0</v>
       </c>
       <c r="P242" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q242" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R242" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S242" s="26" t="str" cm="1">
@@ -8384,15 +8414,15 @@
         <v>0</v>
       </c>
       <c r="P243" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q243" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R243" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S243" s="26" t="str" cm="1">
@@ -8415,15 +8445,15 @@
         <v>0</v>
       </c>
       <c r="P244" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q244" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R244" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S244" s="26" t="str" cm="1">
@@ -8446,15 +8476,15 @@
         <v>0</v>
       </c>
       <c r="P245" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q245" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R245" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S245" s="26" t="str" cm="1">
@@ -8477,15 +8507,15 @@
         <v>0</v>
       </c>
       <c r="P246" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q246" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R246" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S246" s="26" t="str" cm="1">
@@ -8508,15 +8538,15 @@
         <v>0</v>
       </c>
       <c r="P247" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q247" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S247" s="26" t="str" cm="1">
@@ -8539,15 +8569,15 @@
         <v>0</v>
       </c>
       <c r="P248" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q248" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R248" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S248" s="26" t="str" cm="1">
@@ -8570,15 +8600,15 @@
         <v>0</v>
       </c>
       <c r="P249" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q249" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R249" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S249" s="26" t="str" cm="1">
@@ -8601,15 +8631,15 @@
         <v>0</v>
       </c>
       <c r="P250" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q250" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R250" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S250" s="26" t="str" cm="1">
@@ -8632,15 +8662,15 @@
         <v>0</v>
       </c>
       <c r="P251" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q251" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R251" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S251" s="26" t="str" cm="1">
@@ -8663,15 +8693,15 @@
         <v>0</v>
       </c>
       <c r="P252" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q252" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R252" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="S252" s="26" t="str" cm="1">

--- a/Investment Tracking V3.xlsx
+++ b/Investment Tracking V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acmfirm-my.sharepoint.com/personal/isaac_asselstine_treewalk_com/Documents/Documents/Investment Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4733" documentId="8_{B2161804-0EDF-42E0-BE0F-33C496CCEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7286CD7D-4D8F-4066-8596-CBD419379FF2}"/>
+  <xr:revisionPtr revIDLastSave="4738" documentId="8_{B2161804-0EDF-42E0-BE0F-33C496CCEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8A548F-5D12-4798-A3F6-049DD98B3954}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D310D58-D25C-478B-96CD-BDDADD687EF5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5D310D58-D25C-478B-96CD-BDDADD687EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -941,7 +941,7 @@
       </c>
     </row>
     <row r="4" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L4" s="17" cm="1">
+      <c r="L4" s="33" cm="1">
         <f t="array" ref="L4">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D4)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -957,7 +957,7 @@
         <f>H4+M4</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="33">
         <f>I4+L4</f>
         <v>0</v>
       </c>
@@ -988,7 +988,7 @@
       </c>
     </row>
     <row r="5" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L5" s="17" cm="1">
+      <c r="L5" s="33" cm="1">
         <f t="array" ref="L5">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D5)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <f t="shared" ref="P5:P68" si="0">H5+M5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="33">
         <f t="shared" ref="Q5:Q68" si="1">I5+L5</f>
         <v>0</v>
       </c>
@@ -1035,7 +1035,7 @@
       </c>
     </row>
     <row r="6" spans="3:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L6" s="17" cm="1">
+      <c r="L6" s="33" cm="1">
         <f t="array" ref="L6">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D6)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1051,7 +1051,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="45">
-        <f t="shared" ref="Z6:AB6" si="4">Z5+Z4</f>
+        <f t="shared" ref="Z6:AA6" si="4">Z5+Z4</f>
         <v>0</v>
       </c>
       <c r="AA6" s="45">
@@ -1085,7 +1085,7 @@
       </c>
     </row>
     <row r="7" spans="3:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="L7" s="17" cm="1">
+      <c r="L7" s="33" cm="1">
         <f t="array" ref="L7">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D7)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1101,7 +1101,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1116,7 +1116,7 @@
       <c r="V7" s="26"/>
     </row>
     <row r="8" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L8" s="17" cm="1">
+      <c r="L8" s="33" cm="1">
         <f t="array" ref="L8">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D8)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1132,7 +1132,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1147,7 +1147,7 @@
       <c r="V8" s="26"/>
     </row>
     <row r="9" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L9" s="17" cm="1">
+      <c r="L9" s="33" cm="1">
         <f t="array" ref="L9">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D9)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1163,7 +1163,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1178,7 +1178,7 @@
       <c r="V9" s="26"/>
     </row>
     <row r="10" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L10" s="17" cm="1">
+      <c r="L10" s="33" cm="1">
         <f t="array" ref="L10">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D10)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1194,7 +1194,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="V10" s="26"/>
     </row>
     <row r="11" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L11" s="17" cm="1">
+      <c r="L11" s="33" cm="1">
         <f t="array" ref="L11">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D11)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1225,7 +1225,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="V11" s="26"/>
     </row>
     <row r="12" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L12" s="17" cm="1">
+      <c r="L12" s="33" cm="1">
         <f t="array" ref="L12">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D12)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1256,7 +1256,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
       <c r="V12" s="26"/>
     </row>
     <row r="13" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L13" s="17" cm="1">
+      <c r="L13" s="33" cm="1">
         <f t="array" ref="L13">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D13)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1287,7 +1287,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="V13" s="26"/>
     </row>
     <row r="14" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L14" s="17" cm="1">
+      <c r="L14" s="33" cm="1">
         <f t="array" ref="L14">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D14)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="Q14" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="V14" s="26"/>
     </row>
     <row r="15" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L15" s="17" cm="1">
+      <c r="L15" s="33" cm="1">
         <f t="array" ref="L15">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D15)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1349,7 +1349,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="V15" s="26"/>
     </row>
     <row r="16" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="L16" s="17" cm="1">
+      <c r="L16" s="33" cm="1">
         <f t="array" ref="L16">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D16)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1395,7 +1395,7 @@
       <c r="V16" s="26"/>
     </row>
     <row r="17" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L17" s="17" cm="1">
+      <c r="L17" s="33" cm="1">
         <f t="array" ref="L17">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D17)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1411,7 +1411,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="V17" s="26"/>
     </row>
     <row r="18" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L18" s="17" cm="1">
+      <c r="L18" s="33" cm="1">
         <f t="array" ref="L18">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D18)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="Q18" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="V18" s="26"/>
     </row>
     <row r="19" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L19" s="17" cm="1">
+      <c r="L19" s="33" cm="1">
         <f t="array" ref="L19">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D19)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1473,7 +1473,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="V19" s="26"/>
     </row>
     <row r="20" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L20" s="17" cm="1">
+      <c r="L20" s="33" cm="1">
         <f t="array" ref="L20">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D20)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="V20" s="26"/>
     </row>
     <row r="21" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L21" s="17" cm="1">
+      <c r="L21" s="33" cm="1">
         <f t="array" ref="L21">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D21)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1535,7 +1535,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="V21" s="26"/>
     </row>
     <row r="22" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L22" s="17" cm="1">
+      <c r="L22" s="33" cm="1">
         <f t="array" ref="L22">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D22)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1566,7 +1566,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="V22" s="26"/>
     </row>
     <row r="23" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L23" s="17" cm="1">
+      <c r="L23" s="33" cm="1">
         <f t="array" ref="L23">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D23)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="V23" s="26"/>
     </row>
     <row r="24" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L24" s="17" cm="1">
+      <c r="L24" s="33" cm="1">
         <f t="array" ref="L24">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D24)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1628,7 +1628,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1643,7 +1643,7 @@
       <c r="V24" s="26"/>
     </row>
     <row r="25" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L25" s="17" cm="1">
+      <c r="L25" s="33" cm="1">
         <f t="array" ref="L25">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D25)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1659,7 +1659,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1674,7 +1674,7 @@
       <c r="V25" s="26"/>
     </row>
     <row r="26" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L26" s="17" cm="1">
+      <c r="L26" s="33" cm="1">
         <f t="array" ref="L26">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D26)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1690,7 +1690,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="V26" s="26"/>
     </row>
     <row r="27" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L27" s="17" cm="1">
+      <c r="L27" s="33" cm="1">
         <f t="array" ref="L27">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D27)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1721,7 +1721,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="V27" s="26"/>
     </row>
     <row r="28" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L28" s="17" cm="1">
+      <c r="L28" s="33" cm="1">
         <f t="array" ref="L28">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D28)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1752,7 +1752,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="V28" s="26"/>
     </row>
     <row r="29" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L29" s="17" cm="1">
+      <c r="L29" s="33" cm="1">
         <f t="array" ref="L29">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D29)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1783,7 +1783,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1798,7 +1798,7 @@
       <c r="V29" s="26"/>
     </row>
     <row r="30" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L30" s="17" cm="1">
+      <c r="L30" s="33" cm="1">
         <f t="array" ref="L30">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D30)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1814,7 +1814,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="V30" s="26"/>
     </row>
     <row r="31" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L31" s="17" cm="1">
+      <c r="L31" s="33" cm="1">
         <f t="array" ref="L31">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D31)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1845,7 +1845,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1860,7 +1860,7 @@
       <c r="V31" s="26"/>
     </row>
     <row r="32" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L32" s="17" cm="1">
+      <c r="L32" s="33" cm="1">
         <f t="array" ref="L32">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D32)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1876,7 +1876,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="Q32" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="V32" s="26"/>
     </row>
     <row r="33" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L33" s="17" cm="1">
+      <c r="L33" s="33" cm="1">
         <f t="array" ref="L33">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D33)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1907,7 +1907,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1922,7 +1922,7 @@
       <c r="V33" s="26"/>
     </row>
     <row r="34" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L34" s="17" cm="1">
+      <c r="L34" s="33" cm="1">
         <f t="array" ref="L34">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D34)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1938,7 +1938,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1953,7 +1953,7 @@
       <c r="V34" s="26"/>
     </row>
     <row r="35" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L35" s="17" cm="1">
+      <c r="L35" s="33" cm="1">
         <f t="array" ref="L35">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D35)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -1969,7 +1969,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1984,7 +1984,7 @@
       <c r="V35" s="26"/>
     </row>
     <row r="36" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L36" s="17" cm="1">
+      <c r="L36" s="33" cm="1">
         <f t="array" ref="L36">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D36)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2000,7 +2000,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2015,7 +2015,7 @@
       <c r="V36" s="26"/>
     </row>
     <row r="37" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L37" s="17" cm="1">
+      <c r="L37" s="33" cm="1">
         <f t="array" ref="L37">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D37)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2031,7 +2031,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2046,7 +2046,7 @@
       <c r="V37" s="26"/>
     </row>
     <row r="38" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L38" s="17" cm="1">
+      <c r="L38" s="33" cm="1">
         <f t="array" ref="L38">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D38)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2062,7 +2062,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2077,7 +2077,7 @@
       <c r="V38" s="26"/>
     </row>
     <row r="39" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L39" s="17" cm="1">
+      <c r="L39" s="33" cm="1">
         <f t="array" ref="L39">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D39)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2093,7 +2093,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="Q39" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="V39" s="26"/>
     </row>
     <row r="40" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L40" s="17" cm="1">
+      <c r="L40" s="33" cm="1">
         <f t="array" ref="L40">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D40)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="Q40" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="V40" s="26"/>
     </row>
     <row r="41" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L41" s="17" cm="1">
+      <c r="L41" s="33" cm="1">
         <f t="array" ref="L41">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D41)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2155,7 +2155,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="Q41" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2170,7 +2170,7 @@
       <c r="V41" s="26"/>
     </row>
     <row r="42" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L42" s="17" cm="1">
+      <c r="L42" s="33" cm="1">
         <f t="array" ref="L42">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D42)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2186,7 +2186,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="Q42" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="V42" s="26"/>
     </row>
     <row r="43" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L43" s="17" cm="1">
+      <c r="L43" s="33" cm="1">
         <f t="array" ref="L43">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D43)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="Q43" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
       <c r="V43" s="26"/>
     </row>
     <row r="44" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L44" s="17" cm="1">
+      <c r="L44" s="33" cm="1">
         <f t="array" ref="L44">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D44)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2248,7 +2248,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="V44" s="26"/>
     </row>
     <row r="45" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L45" s="17" cm="1">
+      <c r="L45" s="33" cm="1">
         <f t="array" ref="L45">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D45)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2279,7 +2279,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2294,7 +2294,7 @@
       <c r="V45" s="26"/>
     </row>
     <row r="46" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L46" s="17" cm="1">
+      <c r="L46" s="33" cm="1">
         <f t="array" ref="L46">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D46)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2310,7 +2310,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
       <c r="V46" s="26"/>
     </row>
     <row r="47" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L47" s="17" cm="1">
+      <c r="L47" s="33" cm="1">
         <f t="array" ref="L47">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D47)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2341,7 +2341,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
       <c r="V47" s="26"/>
     </row>
     <row r="48" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L48" s="17" cm="1">
+      <c r="L48" s="33" cm="1">
         <f t="array" ref="L48">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D48)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2372,7 +2372,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="V48" s="26"/>
     </row>
     <row r="49" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L49" s="17" cm="1">
+      <c r="L49" s="33" cm="1">
         <f t="array" ref="L49">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D49)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2403,7 +2403,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2418,7 +2418,7 @@
       <c r="V49" s="26"/>
     </row>
     <row r="50" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L50" s="17" cm="1">
+      <c r="L50" s="33" cm="1">
         <f t="array" ref="L50">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D50)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2434,7 +2434,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="V50" s="26"/>
     </row>
     <row r="51" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L51" s="17" cm="1">
+      <c r="L51" s="33" cm="1">
         <f t="array" ref="L51">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D51)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2465,7 +2465,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q51" s="17">
+      <c r="Q51" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="V51" s="26"/>
     </row>
     <row r="52" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L52" s="17" cm="1">
+      <c r="L52" s="33" cm="1">
         <f t="array" ref="L52">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D52)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2496,7 +2496,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q52" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2511,7 +2511,7 @@
       <c r="V52" s="26"/>
     </row>
     <row r="53" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L53" s="17" cm="1">
+      <c r="L53" s="33" cm="1">
         <f t="array" ref="L53">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D53)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2527,7 +2527,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q53" s="17">
+      <c r="Q53" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="V53" s="26"/>
     </row>
     <row r="54" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L54" s="17" cm="1">
+      <c r="L54" s="33" cm="1">
         <f t="array" ref="L54">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D54)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q54" s="17">
+      <c r="Q54" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2573,7 +2573,7 @@
       <c r="V54" s="26"/>
     </row>
     <row r="55" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L55" s="17" cm="1">
+      <c r="L55" s="33" cm="1">
         <f t="array" ref="L55">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D55)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2589,7 +2589,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="V55" s="26"/>
     </row>
     <row r="56" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L56" s="17" cm="1">
+      <c r="L56" s="33" cm="1">
         <f t="array" ref="L56">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D56)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2620,7 +2620,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2635,7 +2635,7 @@
       <c r="V56" s="26"/>
     </row>
     <row r="57" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L57" s="17" cm="1">
+      <c r="L57" s="33" cm="1">
         <f t="array" ref="L57">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D57)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2651,7 +2651,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2666,7 +2666,7 @@
       <c r="V57" s="26"/>
     </row>
     <row r="58" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L58" s="17" cm="1">
+      <c r="L58" s="33" cm="1">
         <f t="array" ref="L58">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D58)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2682,7 +2682,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q58" s="17">
+      <c r="Q58" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="V58" s="26"/>
     </row>
     <row r="59" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L59" s="17" cm="1">
+      <c r="L59" s="33" cm="1">
         <f t="array" ref="L59">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D59)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2713,7 +2713,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2728,7 +2728,7 @@
       <c r="V59" s="26"/>
     </row>
     <row r="60" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L60" s="17" cm="1">
+      <c r="L60" s="33" cm="1">
         <f t="array" ref="L60">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D60)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2744,7 +2744,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2759,7 +2759,7 @@
       <c r="V60" s="26"/>
     </row>
     <row r="61" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L61" s="17" cm="1">
+      <c r="L61" s="33" cm="1">
         <f t="array" ref="L61">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D61)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2775,7 +2775,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2790,7 +2790,7 @@
       <c r="V61" s="26"/>
     </row>
     <row r="62" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L62" s="17" cm="1">
+      <c r="L62" s="33" cm="1">
         <f t="array" ref="L62">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D62)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2806,7 +2806,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q62" s="17">
+      <c r="Q62" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="V62" s="26"/>
     </row>
     <row r="63" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L63" s="17" cm="1">
+      <c r="L63" s="33" cm="1">
         <f t="array" ref="L63">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D63)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2837,7 +2837,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q63" s="17">
+      <c r="Q63" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="V63" s="26"/>
     </row>
     <row r="64" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L64" s="17" cm="1">
+      <c r="L64" s="33" cm="1">
         <f t="array" ref="L64">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D64)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2868,7 +2868,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2883,7 +2883,7 @@
       <c r="V64" s="26"/>
     </row>
     <row r="65" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L65" s="17" cm="1">
+      <c r="L65" s="33" cm="1">
         <f t="array" ref="L65">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D65)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2899,7 +2899,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q65" s="17">
+      <c r="Q65" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2914,7 +2914,7 @@
       <c r="V65" s="26"/>
     </row>
     <row r="66" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L66" s="17" cm="1">
+      <c r="L66" s="33" cm="1">
         <f t="array" ref="L66">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D66)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2930,7 +2930,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q66" s="17">
+      <c r="Q66" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="V66" s="26"/>
     </row>
     <row r="67" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L67" s="17" cm="1">
+      <c r="L67" s="33" cm="1">
         <f t="array" ref="L67">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D67)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2961,7 +2961,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q67" s="17">
+      <c r="Q67" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2976,7 +2976,7 @@
       <c r="V67" s="26"/>
     </row>
     <row r="68" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L68" s="17" cm="1">
+      <c r="L68" s="33" cm="1">
         <f t="array" ref="L68">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D68)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -2992,7 +2992,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q68" s="17">
+      <c r="Q68" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3007,7 +3007,7 @@
       <c r="V68" s="26"/>
     </row>
     <row r="69" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L69" s="17" cm="1">
+      <c r="L69" s="33" cm="1">
         <f t="array" ref="L69">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D69)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3023,7 +3023,7 @@
         <f t="shared" ref="P69:P132" si="5">H69+M69</f>
         <v>0</v>
       </c>
-      <c r="Q69" s="17">
+      <c r="Q69" s="33">
         <f t="shared" ref="Q69:Q132" si="6">I69+L69</f>
         <v>0</v>
       </c>
@@ -3038,7 +3038,7 @@
       <c r="V69" s="26"/>
     </row>
     <row r="70" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L70" s="17" cm="1">
+      <c r="L70" s="33" cm="1">
         <f t="array" ref="L70">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D70)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3054,7 +3054,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="17">
+      <c r="Q70" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="V70" s="26"/>
     </row>
     <row r="71" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L71" s="17" cm="1">
+      <c r="L71" s="33" cm="1">
         <f t="array" ref="L71">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D71)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3085,7 +3085,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q71" s="17">
+      <c r="Q71" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="V71" s="26"/>
     </row>
     <row r="72" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L72" s="17" cm="1">
+      <c r="L72" s="33" cm="1">
         <f t="array" ref="L72">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D72)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3116,7 +3116,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q72" s="17">
+      <c r="Q72" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       <c r="V72" s="26"/>
     </row>
     <row r="73" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L73" s="17" cm="1">
+      <c r="L73" s="33" cm="1">
         <f t="array" ref="L73">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D73)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3147,7 +3147,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q73" s="17">
+      <c r="Q73" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3162,7 +3162,7 @@
       <c r="V73" s="26"/>
     </row>
     <row r="74" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L74" s="17" cm="1">
+      <c r="L74" s="33" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D74)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3178,7 +3178,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q74" s="17">
+      <c r="Q74" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="V74" s="26"/>
     </row>
     <row r="75" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L75" s="17" cm="1">
+      <c r="L75" s="33" cm="1">
         <f t="array" ref="L75">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D75)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3209,7 +3209,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q75" s="17">
+      <c r="Q75" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="V75" s="26"/>
     </row>
     <row r="76" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L76" s="17" cm="1">
+      <c r="L76" s="33" cm="1">
         <f t="array" ref="L76">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D76)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3240,7 +3240,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q76" s="17">
+      <c r="Q76" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3255,7 +3255,7 @@
       <c r="V76" s="26"/>
     </row>
     <row r="77" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L77" s="17" cm="1">
+      <c r="L77" s="33" cm="1">
         <f t="array" ref="L77">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D77)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3271,7 +3271,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q77" s="17">
+      <c r="Q77" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3286,7 +3286,7 @@
       <c r="V77" s="26"/>
     </row>
     <row r="78" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L78" s="17" cm="1">
+      <c r="L78" s="33" cm="1">
         <f t="array" ref="L78">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D78)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3302,7 +3302,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q78" s="17">
+      <c r="Q78" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
       <c r="V78" s="26"/>
     </row>
     <row r="79" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L79" s="17" cm="1">
+      <c r="L79" s="33" cm="1">
         <f t="array" ref="L79">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D79)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q79" s="17">
+      <c r="Q79" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3348,7 +3348,7 @@
       <c r="V79" s="26"/>
     </row>
     <row r="80" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L80" s="17" cm="1">
+      <c r="L80" s="33" cm="1">
         <f t="array" ref="L80">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D80)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3364,7 +3364,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q80" s="17">
+      <c r="Q80" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3379,7 +3379,7 @@
       <c r="V80" s="26"/>
     </row>
     <row r="81" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L81" s="17" cm="1">
+      <c r="L81" s="33" cm="1">
         <f t="array" ref="L81">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D81)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3395,7 +3395,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q81" s="17">
+      <c r="Q81" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="V81" s="26"/>
     </row>
     <row r="82" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L82" s="17" cm="1">
+      <c r="L82" s="33" cm="1">
         <f t="array" ref="L82">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D82)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3426,7 +3426,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q82" s="17">
+      <c r="Q82" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="V82" s="26"/>
     </row>
     <row r="83" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L83" s="17" cm="1">
+      <c r="L83" s="33" cm="1">
         <f t="array" ref="L83">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D83)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3457,7 +3457,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q83" s="17">
+      <c r="Q83" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3472,7 +3472,7 @@
       <c r="V83" s="26"/>
     </row>
     <row r="84" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L84" s="17" cm="1">
+      <c r="L84" s="33" cm="1">
         <f t="array" ref="L84">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D84)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3488,7 +3488,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q84" s="17">
+      <c r="Q84" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="V84" s="26"/>
     </row>
     <row r="85" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L85" s="17" cm="1">
+      <c r="L85" s="33" cm="1">
         <f t="array" ref="L85">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D85)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3519,7 +3519,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q85" s="17">
+      <c r="Q85" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3534,7 +3534,7 @@
       <c r="V85" s="26"/>
     </row>
     <row r="86" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L86" s="17" cm="1">
+      <c r="L86" s="33" cm="1">
         <f t="array" ref="L86">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D86)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3550,7 +3550,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q86" s="17">
+      <c r="Q86" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="V86" s="26"/>
     </row>
     <row r="87" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L87" s="17" cm="1">
+      <c r="L87" s="33" cm="1">
         <f t="array" ref="L87">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D87)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3581,7 +3581,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q87" s="17">
+      <c r="Q87" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3596,7 +3596,7 @@
       <c r="V87" s="26"/>
     </row>
     <row r="88" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L88" s="17" cm="1">
+      <c r="L88" s="33" cm="1">
         <f t="array" ref="L88">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D88)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3612,7 +3612,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q88" s="17">
+      <c r="Q88" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3627,7 +3627,7 @@
       <c r="V88" s="26"/>
     </row>
     <row r="89" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L89" s="17" cm="1">
+      <c r="L89" s="33" cm="1">
         <f t="array" ref="L89">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D89)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3643,7 +3643,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q89" s="17">
+      <c r="Q89" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="V89" s="26"/>
     </row>
     <row r="90" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L90" s="17" cm="1">
+      <c r="L90" s="33" cm="1">
         <f t="array" ref="L90">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D90)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3674,7 +3674,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q90" s="17">
+      <c r="Q90" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="V90" s="26"/>
     </row>
     <row r="91" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L91" s="17" cm="1">
+      <c r="L91" s="33" cm="1">
         <f t="array" ref="L91">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D91)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3705,7 +3705,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q91" s="17">
+      <c r="Q91" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3720,7 +3720,7 @@
       <c r="V91" s="26"/>
     </row>
     <row r="92" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L92" s="17" cm="1">
+      <c r="L92" s="33" cm="1">
         <f t="array" ref="L92">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D92)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3736,7 +3736,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q92" s="17">
+      <c r="Q92" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="V92" s="26"/>
     </row>
     <row r="93" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L93" s="17" cm="1">
+      <c r="L93" s="33" cm="1">
         <f t="array" ref="L93">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D93)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3767,7 +3767,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="17">
+      <c r="Q93" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="V93" s="26"/>
     </row>
     <row r="94" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L94" s="17" cm="1">
+      <c r="L94" s="33" cm="1">
         <f t="array" ref="L94">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D94)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3798,7 +3798,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q94" s="17">
+      <c r="Q94" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3813,7 +3813,7 @@
       <c r="V94" s="26"/>
     </row>
     <row r="95" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L95" s="17" cm="1">
+      <c r="L95" s="33" cm="1">
         <f t="array" ref="L95">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D95)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3829,7 +3829,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q95" s="17">
+      <c r="Q95" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="V95" s="26"/>
     </row>
     <row r="96" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L96" s="17" cm="1">
+      <c r="L96" s="33" cm="1">
         <f t="array" ref="L96">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D96)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3860,7 +3860,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q96" s="17">
+      <c r="Q96" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="V96" s="26"/>
     </row>
     <row r="97" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L97" s="17" cm="1">
+      <c r="L97" s="33" cm="1">
         <f t="array" ref="L97">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D97)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3891,7 +3891,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q97" s="17">
+      <c r="Q97" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3906,7 +3906,7 @@
       <c r="V97" s="26"/>
     </row>
     <row r="98" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L98" s="17" cm="1">
+      <c r="L98" s="33" cm="1">
         <f t="array" ref="L98">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D98)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3922,7 +3922,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q98" s="17">
+      <c r="Q98" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3937,7 +3937,7 @@
       <c r="V98" s="26"/>
     </row>
     <row r="99" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L99" s="17" cm="1">
+      <c r="L99" s="33" cm="1">
         <f t="array" ref="L99">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D99)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3953,7 +3953,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q99" s="17">
+      <c r="Q99" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="V99" s="26"/>
     </row>
     <row r="100" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L100" s="17" cm="1">
+      <c r="L100" s="33" cm="1">
         <f t="array" ref="L100">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D100)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -3984,7 +3984,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q100" s="17">
+      <c r="Q100" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -3999,7 +3999,7 @@
       <c r="V100" s="26"/>
     </row>
     <row r="101" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L101" s="17" cm="1">
+      <c r="L101" s="33" cm="1">
         <f t="array" ref="L101">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D101)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4015,7 +4015,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q101" s="17">
+      <c r="Q101" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="V101" s="26"/>
     </row>
     <row r="102" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L102" s="17" cm="1">
+      <c r="L102" s="33" cm="1">
         <f t="array" ref="L102">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D102)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4046,7 +4046,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q102" s="17">
+      <c r="Q102" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4061,7 +4061,7 @@
       <c r="V102" s="26"/>
     </row>
     <row r="103" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L103" s="17" cm="1">
+      <c r="L103" s="33" cm="1">
         <f t="array" ref="L103">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D103)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4077,7 +4077,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q103" s="17">
+      <c r="Q103" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4092,7 +4092,7 @@
       <c r="V103" s="26"/>
     </row>
     <row r="104" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L104" s="17" cm="1">
+      <c r="L104" s="33" cm="1">
         <f t="array" ref="L104">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D104)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4108,7 +4108,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q104" s="17">
+      <c r="Q104" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="V104" s="26"/>
     </row>
     <row r="105" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L105" s="17" cm="1">
+      <c r="L105" s="33" cm="1">
         <f t="array" ref="L105">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D105)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4139,7 +4139,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q105" s="17">
+      <c r="Q105" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="V105" s="26"/>
     </row>
     <row r="106" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L106" s="17" cm="1">
+      <c r="L106" s="33" cm="1">
         <f t="array" ref="L106">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D106)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4170,7 +4170,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q106" s="17">
+      <c r="Q106" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4185,7 +4185,7 @@
       <c r="V106" s="26"/>
     </row>
     <row r="107" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L107" s="17" cm="1">
+      <c r="L107" s="33" cm="1">
         <f t="array" ref="L107">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D107)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4201,7 +4201,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q107" s="17">
+      <c r="Q107" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4216,7 +4216,7 @@
       <c r="V107" s="26"/>
     </row>
     <row r="108" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L108" s="17" cm="1">
+      <c r="L108" s="33" cm="1">
         <f t="array" ref="L108">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D108)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4232,7 +4232,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q108" s="17">
+      <c r="Q108" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4247,7 +4247,7 @@
       <c r="V108" s="26"/>
     </row>
     <row r="109" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L109" s="17" cm="1">
+      <c r="L109" s="33" cm="1">
         <f t="array" ref="L109">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D109)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4263,7 +4263,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q109" s="17">
+      <c r="Q109" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4278,7 +4278,7 @@
       <c r="V109" s="26"/>
     </row>
     <row r="110" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L110" s="17" cm="1">
+      <c r="L110" s="33" cm="1">
         <f t="array" ref="L110">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D110)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4294,7 +4294,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q110" s="17">
+      <c r="Q110" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4309,7 +4309,7 @@
       <c r="V110" s="26"/>
     </row>
     <row r="111" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L111" s="17" cm="1">
+      <c r="L111" s="33" cm="1">
         <f t="array" ref="L111">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D111)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q111" s="17">
+      <c r="Q111" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4340,7 +4340,7 @@
       <c r="V111" s="26"/>
     </row>
     <row r="112" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L112" s="17" cm="1">
+      <c r="L112" s="33" cm="1">
         <f t="array" ref="L112">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D112)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4356,7 +4356,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q112" s="17">
+      <c r="Q112" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4371,7 +4371,7 @@
       <c r="V112" s="26"/>
     </row>
     <row r="113" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L113" s="17" cm="1">
+      <c r="L113" s="33" cm="1">
         <f t="array" ref="L113">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D113)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4387,7 +4387,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q113" s="17">
+      <c r="Q113" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="V113" s="26"/>
     </row>
     <row r="114" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L114" s="17" cm="1">
+      <c r="L114" s="33" cm="1">
         <f t="array" ref="L114">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D114)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4418,7 +4418,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q114" s="17">
+      <c r="Q114" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="V114" s="26"/>
     </row>
     <row r="115" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L115" s="17" cm="1">
+      <c r="L115" s="33" cm="1">
         <f t="array" ref="L115">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D115)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4449,7 +4449,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q115" s="17">
+      <c r="Q115" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4464,7 +4464,7 @@
       <c r="V115" s="26"/>
     </row>
     <row r="116" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L116" s="17" cm="1">
+      <c r="L116" s="33" cm="1">
         <f t="array" ref="L116">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D116)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4480,7 +4480,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q116" s="17">
+      <c r="Q116" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="V116" s="26"/>
     </row>
     <row r="117" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L117" s="17" cm="1">
+      <c r="L117" s="33" cm="1">
         <f t="array" ref="L117">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D117)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4511,7 +4511,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q117" s="17">
+      <c r="Q117" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="V117" s="26"/>
     </row>
     <row r="118" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L118" s="17" cm="1">
+      <c r="L118" s="33" cm="1">
         <f t="array" ref="L118">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D118)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4542,7 +4542,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q118" s="17">
+      <c r="Q118" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4557,7 +4557,7 @@
       <c r="V118" s="26"/>
     </row>
     <row r="119" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L119" s="17" cm="1">
+      <c r="L119" s="33" cm="1">
         <f t="array" ref="L119">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D119)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4573,7 +4573,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q119" s="17">
+      <c r="Q119" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4588,7 +4588,7 @@
       <c r="V119" s="26"/>
     </row>
     <row r="120" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L120" s="17" cm="1">
+      <c r="L120" s="33" cm="1">
         <f t="array" ref="L120">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D120)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4604,7 +4604,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q120" s="17">
+      <c r="Q120" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="V120" s="26"/>
     </row>
     <row r="121" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L121" s="17" cm="1">
+      <c r="L121" s="33" cm="1">
         <f t="array" ref="L121">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D121)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4635,7 +4635,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q121" s="17">
+      <c r="Q121" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4650,7 +4650,7 @@
       <c r="V121" s="26"/>
     </row>
     <row r="122" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L122" s="17" cm="1">
+      <c r="L122" s="33" cm="1">
         <f t="array" ref="L122">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D122)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4666,7 +4666,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q122" s="17">
+      <c r="Q122" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="V122" s="26"/>
     </row>
     <row r="123" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L123" s="17" cm="1">
+      <c r="L123" s="33" cm="1">
         <f t="array" ref="L123">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D123)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4697,7 +4697,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q123" s="17">
+      <c r="Q123" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4712,7 +4712,7 @@
       <c r="V123" s="26"/>
     </row>
     <row r="124" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L124" s="17" cm="1">
+      <c r="L124" s="33" cm="1">
         <f t="array" ref="L124">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D124)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4728,7 +4728,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q124" s="17">
+      <c r="Q124" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4743,7 +4743,7 @@
       <c r="V124" s="26"/>
     </row>
     <row r="125" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L125" s="17" cm="1">
+      <c r="L125" s="33" cm="1">
         <f t="array" ref="L125">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D125)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4759,7 +4759,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q125" s="17">
+      <c r="Q125" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4774,7 +4774,7 @@
       <c r="V125" s="26"/>
     </row>
     <row r="126" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L126" s="17" cm="1">
+      <c r="L126" s="33" cm="1">
         <f t="array" ref="L126">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D126)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4790,7 +4790,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q126" s="17">
+      <c r="Q126" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4805,7 +4805,7 @@
       <c r="V126" s="26"/>
     </row>
     <row r="127" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L127" s="17" cm="1">
+      <c r="L127" s="33" cm="1">
         <f t="array" ref="L127">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D127)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4821,7 +4821,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q127" s="17">
+      <c r="Q127" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="V127" s="26"/>
     </row>
     <row r="128" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L128" s="17" cm="1">
+      <c r="L128" s="33" cm="1">
         <f t="array" ref="L128">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D128)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4852,7 +4852,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q128" s="17">
+      <c r="Q128" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4867,7 +4867,7 @@
       <c r="V128" s="26"/>
     </row>
     <row r="129" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L129" s="17" cm="1">
+      <c r="L129" s="33" cm="1">
         <f t="array" ref="L129">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D129)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4883,7 +4883,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q129" s="17">
+      <c r="Q129" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4898,7 +4898,7 @@
       <c r="V129" s="26"/>
     </row>
     <row r="130" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L130" s="17" cm="1">
+      <c r="L130" s="33" cm="1">
         <f t="array" ref="L130">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D130)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4914,7 +4914,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q130" s="17">
+      <c r="Q130" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4929,7 +4929,7 @@
       <c r="V130" s="26"/>
     </row>
     <row r="131" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L131" s="17" cm="1">
+      <c r="L131" s="33" cm="1">
         <f t="array" ref="L131">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D131)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4945,7 +4945,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q131" s="17">
+      <c r="Q131" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="V131" s="26"/>
     </row>
     <row r="132" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L132" s="17" cm="1">
+      <c r="L132" s="33" cm="1">
         <f t="array" ref="L132">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D132)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -4976,7 +4976,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q132" s="17">
+      <c r="Q132" s="33">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4991,7 +4991,7 @@
       <c r="V132" s="26"/>
     </row>
     <row r="133" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L133" s="17" cm="1">
+      <c r="L133" s="33" cm="1">
         <f t="array" ref="L133">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D133)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5007,7 +5007,7 @@
         <f t="shared" ref="P133:P196" si="8">H133+M133</f>
         <v>0</v>
       </c>
-      <c r="Q133" s="17">
+      <c r="Q133" s="33">
         <f t="shared" ref="Q133:Q196" si="9">I133+L133</f>
         <v>0</v>
       </c>
@@ -5022,7 +5022,7 @@
       <c r="V133" s="26"/>
     </row>
     <row r="134" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L134" s="17" cm="1">
+      <c r="L134" s="33" cm="1">
         <f t="array" ref="L134">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D134)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5038,7 +5038,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q134" s="17">
+      <c r="Q134" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5053,7 +5053,7 @@
       <c r="V134" s="26"/>
     </row>
     <row r="135" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L135" s="17" cm="1">
+      <c r="L135" s="33" cm="1">
         <f t="array" ref="L135">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D135)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5069,7 +5069,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q135" s="17">
+      <c r="Q135" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5084,7 +5084,7 @@
       <c r="V135" s="26"/>
     </row>
     <row r="136" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L136" s="17" cm="1">
+      <c r="L136" s="33" cm="1">
         <f t="array" ref="L136">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D136)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5100,7 +5100,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q136" s="17">
+      <c r="Q136" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="V136" s="26"/>
     </row>
     <row r="137" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L137" s="17" cm="1">
+      <c r="L137" s="33" cm="1">
         <f t="array" ref="L137">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D137)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5131,7 +5131,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q137" s="17">
+      <c r="Q137" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5146,7 +5146,7 @@
       <c r="V137" s="26"/>
     </row>
     <row r="138" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L138" s="17" cm="1">
+      <c r="L138" s="33" cm="1">
         <f t="array" ref="L138">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D138)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5162,7 +5162,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q138" s="17">
+      <c r="Q138" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5177,7 +5177,7 @@
       <c r="V138" s="26"/>
     </row>
     <row r="139" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L139" s="17" cm="1">
+      <c r="L139" s="33" cm="1">
         <f t="array" ref="L139">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D139)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5193,7 +5193,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q139" s="17">
+      <c r="Q139" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="V139" s="26"/>
     </row>
     <row r="140" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L140" s="17" cm="1">
+      <c r="L140" s="33" cm="1">
         <f t="array" ref="L140">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D140)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5224,7 +5224,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q140" s="17">
+      <c r="Q140" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5239,7 +5239,7 @@
       <c r="V140" s="26"/>
     </row>
     <row r="141" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L141" s="17" cm="1">
+      <c r="L141" s="33" cm="1">
         <f t="array" ref="L141">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D141)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5255,7 +5255,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q141" s="17">
+      <c r="Q141" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="V141" s="26"/>
     </row>
     <row r="142" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L142" s="17" cm="1">
+      <c r="L142" s="33" cm="1">
         <f t="array" ref="L142">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D142)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5286,7 +5286,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q142" s="17">
+      <c r="Q142" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5301,7 +5301,7 @@
       <c r="V142" s="26"/>
     </row>
     <row r="143" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L143" s="17" cm="1">
+      <c r="L143" s="33" cm="1">
         <f t="array" ref="L143">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D143)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5317,7 +5317,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q143" s="17">
+      <c r="Q143" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5332,7 +5332,7 @@
       <c r="V143" s="26"/>
     </row>
     <row r="144" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L144" s="17" cm="1">
+      <c r="L144" s="33" cm="1">
         <f t="array" ref="L144">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D144)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5348,7 +5348,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q144" s="17">
+      <c r="Q144" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5363,7 +5363,7 @@
       <c r="V144" s="26"/>
     </row>
     <row r="145" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L145" s="17" cm="1">
+      <c r="L145" s="33" cm="1">
         <f t="array" ref="L145">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D145)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5379,7 +5379,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q145" s="17">
+      <c r="Q145" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="V145" s="26"/>
     </row>
     <row r="146" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L146" s="17" cm="1">
+      <c r="L146" s="33" cm="1">
         <f t="array" ref="L146">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D146)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5410,7 +5410,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q146" s="17">
+      <c r="Q146" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5425,7 +5425,7 @@
       <c r="V146" s="26"/>
     </row>
     <row r="147" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L147" s="17" cm="1">
+      <c r="L147" s="33" cm="1">
         <f t="array" ref="L147">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D147)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5441,7 +5441,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q147" s="17">
+      <c r="Q147" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5456,7 +5456,7 @@
       <c r="V147" s="26"/>
     </row>
     <row r="148" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L148" s="17" cm="1">
+      <c r="L148" s="33" cm="1">
         <f t="array" ref="L148">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D148)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5472,7 +5472,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q148" s="17">
+      <c r="Q148" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5487,7 +5487,7 @@
       <c r="V148" s="26"/>
     </row>
     <row r="149" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L149" s="17" cm="1">
+      <c r="L149" s="33" cm="1">
         <f t="array" ref="L149">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D149)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5503,7 +5503,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q149" s="17">
+      <c r="Q149" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="V149" s="26"/>
     </row>
     <row r="150" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L150" s="17" cm="1">
+      <c r="L150" s="33" cm="1">
         <f t="array" ref="L150">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D150)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5534,7 +5534,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q150" s="17">
+      <c r="Q150" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5549,7 +5549,7 @@
       <c r="V150" s="26"/>
     </row>
     <row r="151" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L151" s="17" cm="1">
+      <c r="L151" s="33" cm="1">
         <f t="array" ref="L151">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D151)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5565,7 +5565,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q151" s="17">
+      <c r="Q151" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5580,7 +5580,7 @@
       <c r="V151" s="26"/>
     </row>
     <row r="152" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L152" s="17" cm="1">
+      <c r="L152" s="33" cm="1">
         <f t="array" ref="L152">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D152)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5596,7 +5596,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q152" s="17">
+      <c r="Q152" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="V152" s="26"/>
     </row>
     <row r="153" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L153" s="17" cm="1">
+      <c r="L153" s="33" cm="1">
         <f t="array" ref="L153">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D153)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5627,7 +5627,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q153" s="17">
+      <c r="Q153" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5642,7 +5642,7 @@
       <c r="V153" s="26"/>
     </row>
     <row r="154" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L154" s="17" cm="1">
+      <c r="L154" s="33" cm="1">
         <f t="array" ref="L154">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D154)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5658,7 +5658,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q154" s="17">
+      <c r="Q154" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5673,7 +5673,7 @@
       <c r="V154" s="26"/>
     </row>
     <row r="155" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L155" s="17" cm="1">
+      <c r="L155" s="33" cm="1">
         <f t="array" ref="L155">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D155)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5689,7 +5689,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q155" s="17">
+      <c r="Q155" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5704,7 +5704,7 @@
       <c r="V155" s="26"/>
     </row>
     <row r="156" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L156" s="17" cm="1">
+      <c r="L156" s="33" cm="1">
         <f t="array" ref="L156">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D156)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5720,7 +5720,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q156" s="17">
+      <c r="Q156" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5735,7 +5735,7 @@
       <c r="V156" s="26"/>
     </row>
     <row r="157" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L157" s="17" cm="1">
+      <c r="L157" s="33" cm="1">
         <f t="array" ref="L157">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D157)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5751,7 +5751,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q157" s="17">
+      <c r="Q157" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5766,7 +5766,7 @@
       <c r="V157" s="26"/>
     </row>
     <row r="158" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L158" s="17" cm="1">
+      <c r="L158" s="33" cm="1">
         <f t="array" ref="L158">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D158)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5782,7 +5782,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q158" s="17">
+      <c r="Q158" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5797,7 +5797,7 @@
       <c r="V158" s="26"/>
     </row>
     <row r="159" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L159" s="17" cm="1">
+      <c r="L159" s="33" cm="1">
         <f t="array" ref="L159">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D159)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5813,7 +5813,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q159" s="17">
+      <c r="Q159" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5828,7 +5828,7 @@
       <c r="V159" s="26"/>
     </row>
     <row r="160" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L160" s="17" cm="1">
+      <c r="L160" s="33" cm="1">
         <f t="array" ref="L160">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D160)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5844,7 +5844,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q160" s="17">
+      <c r="Q160" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5859,7 +5859,7 @@
       <c r="V160" s="26"/>
     </row>
     <row r="161" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L161" s="17" cm="1">
+      <c r="L161" s="33" cm="1">
         <f t="array" ref="L161">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D161)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5875,7 +5875,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q161" s="17">
+      <c r="Q161" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5890,7 +5890,7 @@
       <c r="V161" s="26"/>
     </row>
     <row r="162" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L162" s="17" cm="1">
+      <c r="L162" s="33" cm="1">
         <f t="array" ref="L162">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D162)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5906,7 +5906,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q162" s="17">
+      <c r="Q162" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5921,7 +5921,7 @@
       <c r="V162" s="26"/>
     </row>
     <row r="163" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L163" s="17" cm="1">
+      <c r="L163" s="33" cm="1">
         <f t="array" ref="L163">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D163)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5937,7 +5937,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q163" s="17">
+      <c r="Q163" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5952,7 +5952,7 @@
       <c r="V163" s="26"/>
     </row>
     <row r="164" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L164" s="17" cm="1">
+      <c r="L164" s="33" cm="1">
         <f t="array" ref="L164">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D164)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5968,7 +5968,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q164" s="17">
+      <c r="Q164" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5983,7 +5983,7 @@
       <c r="V164" s="26"/>
     </row>
     <row r="165" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L165" s="17" cm="1">
+      <c r="L165" s="33" cm="1">
         <f t="array" ref="L165">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D165)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -5999,7 +5999,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q165" s="17">
+      <c r="Q165" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="V165" s="26"/>
     </row>
     <row r="166" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L166" s="17" cm="1">
+      <c r="L166" s="33" cm="1">
         <f t="array" ref="L166">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D166)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6030,7 +6030,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q166" s="17">
+      <c r="Q166" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6045,7 +6045,7 @@
       <c r="V166" s="26"/>
     </row>
     <row r="167" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L167" s="17" cm="1">
+      <c r="L167" s="33" cm="1">
         <f t="array" ref="L167">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D167)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6061,7 +6061,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q167" s="17">
+      <c r="Q167" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6076,7 +6076,7 @@
       <c r="V167" s="26"/>
     </row>
     <row r="168" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L168" s="17" cm="1">
+      <c r="L168" s="33" cm="1">
         <f t="array" ref="L168">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D168)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6092,7 +6092,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q168" s="17">
+      <c r="Q168" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="V168" s="26"/>
     </row>
     <row r="169" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L169" s="17" cm="1">
+      <c r="L169" s="33" cm="1">
         <f t="array" ref="L169">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D169)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6123,7 +6123,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q169" s="17">
+      <c r="Q169" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="V169" s="26"/>
     </row>
     <row r="170" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L170" s="17" cm="1">
+      <c r="L170" s="33" cm="1">
         <f t="array" ref="L170">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D170)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6154,7 +6154,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q170" s="17">
+      <c r="Q170" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6169,7 +6169,7 @@
       <c r="V170" s="26"/>
     </row>
     <row r="171" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L171" s="17" cm="1">
+      <c r="L171" s="33" cm="1">
         <f t="array" ref="L171">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D171)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6185,7 +6185,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q171" s="17">
+      <c r="Q171" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6200,7 +6200,7 @@
       <c r="V171" s="26"/>
     </row>
     <row r="172" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L172" s="17" cm="1">
+      <c r="L172" s="33" cm="1">
         <f t="array" ref="L172">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D172)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6216,7 +6216,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q172" s="17">
+      <c r="Q172" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6231,7 +6231,7 @@
       <c r="V172" s="26"/>
     </row>
     <row r="173" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L173" s="17" cm="1">
+      <c r="L173" s="33" cm="1">
         <f t="array" ref="L173">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D173)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6247,7 +6247,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q173" s="17">
+      <c r="Q173" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6262,7 +6262,7 @@
       <c r="V173" s="26"/>
     </row>
     <row r="174" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L174" s="17" cm="1">
+      <c r="L174" s="33" cm="1">
         <f t="array" ref="L174">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D174)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6278,7 +6278,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q174" s="17">
+      <c r="Q174" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6293,7 +6293,7 @@
       <c r="V174" s="26"/>
     </row>
     <row r="175" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L175" s="17" cm="1">
+      <c r="L175" s="33" cm="1">
         <f t="array" ref="L175">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D175)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6309,7 +6309,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q175" s="17">
+      <c r="Q175" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6324,7 +6324,7 @@
       <c r="V175" s="26"/>
     </row>
     <row r="176" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L176" s="17" cm="1">
+      <c r="L176" s="33" cm="1">
         <f t="array" ref="L176">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D176)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6340,7 +6340,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q176" s="17">
+      <c r="Q176" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6355,7 +6355,7 @@
       <c r="V176" s="26"/>
     </row>
     <row r="177" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L177" s="17" cm="1">
+      <c r="L177" s="33" cm="1">
         <f t="array" ref="L177">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D177)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6371,7 +6371,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q177" s="17">
+      <c r="Q177" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6386,7 +6386,7 @@
       <c r="V177" s="26"/>
     </row>
     <row r="178" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L178" s="17" cm="1">
+      <c r="L178" s="33" cm="1">
         <f t="array" ref="L178">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D178)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6402,7 +6402,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q178" s="17">
+      <c r="Q178" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6417,7 +6417,7 @@
       <c r="V178" s="26"/>
     </row>
     <row r="179" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L179" s="17" cm="1">
+      <c r="L179" s="33" cm="1">
         <f t="array" ref="L179">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D179)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6433,7 +6433,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q179" s="17">
+      <c r="Q179" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6448,7 +6448,7 @@
       <c r="V179" s="26"/>
     </row>
     <row r="180" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L180" s="17" cm="1">
+      <c r="L180" s="33" cm="1">
         <f t="array" ref="L180">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D180)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6464,7 +6464,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q180" s="17">
+      <c r="Q180" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6479,7 +6479,7 @@
       <c r="V180" s="26"/>
     </row>
     <row r="181" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L181" s="17" cm="1">
+      <c r="L181" s="33" cm="1">
         <f t="array" ref="L181">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D181)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6495,7 +6495,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q181" s="17">
+      <c r="Q181" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6510,7 +6510,7 @@
       <c r="V181" s="26"/>
     </row>
     <row r="182" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L182" s="17" cm="1">
+      <c r="L182" s="33" cm="1">
         <f t="array" ref="L182">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D182)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6526,7 +6526,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q182" s="17">
+      <c r="Q182" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6541,7 +6541,7 @@
       <c r="V182" s="26"/>
     </row>
     <row r="183" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L183" s="17" cm="1">
+      <c r="L183" s="33" cm="1">
         <f t="array" ref="L183">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D183)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6557,7 +6557,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q183" s="17">
+      <c r="Q183" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6572,7 +6572,7 @@
       <c r="V183" s="26"/>
     </row>
     <row r="184" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L184" s="17" cm="1">
+      <c r="L184" s="33" cm="1">
         <f t="array" ref="L184">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D184)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6588,7 +6588,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q184" s="17">
+      <c r="Q184" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6603,7 +6603,7 @@
       <c r="V184" s="26"/>
     </row>
     <row r="185" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L185" s="17" cm="1">
+      <c r="L185" s="33" cm="1">
         <f t="array" ref="L185">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D185)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6619,7 +6619,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q185" s="17">
+      <c r="Q185" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6634,7 +6634,7 @@
       <c r="V185" s="26"/>
     </row>
     <row r="186" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L186" s="17" cm="1">
+      <c r="L186" s="33" cm="1">
         <f t="array" ref="L186">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D186)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6650,7 +6650,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q186" s="17">
+      <c r="Q186" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6665,7 +6665,7 @@
       <c r="V186" s="26"/>
     </row>
     <row r="187" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L187" s="17" cm="1">
+      <c r="L187" s="33" cm="1">
         <f t="array" ref="L187">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D187)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6681,7 +6681,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q187" s="17">
+      <c r="Q187" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="V187" s="26"/>
     </row>
     <row r="188" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L188" s="17" cm="1">
+      <c r="L188" s="33" cm="1">
         <f t="array" ref="L188">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D188)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6712,7 +6712,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q188" s="17">
+      <c r="Q188" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6727,7 +6727,7 @@
       <c r="V188" s="26"/>
     </row>
     <row r="189" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L189" s="17" cm="1">
+      <c r="L189" s="33" cm="1">
         <f t="array" ref="L189">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D189)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6743,7 +6743,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q189" s="17">
+      <c r="Q189" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="V189" s="26"/>
     </row>
     <row r="190" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L190" s="17" cm="1">
+      <c r="L190" s="33" cm="1">
         <f t="array" ref="L190">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D190)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6774,7 +6774,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q190" s="17">
+      <c r="Q190" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6789,7 +6789,7 @@
       <c r="V190" s="26"/>
     </row>
     <row r="191" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L191" s="17" cm="1">
+      <c r="L191" s="33" cm="1">
         <f t="array" ref="L191">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D191)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6805,7 +6805,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q191" s="17">
+      <c r="Q191" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="V191" s="26"/>
     </row>
     <row r="192" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L192" s="17" cm="1">
+      <c r="L192" s="33" cm="1">
         <f t="array" ref="L192">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D192)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6836,7 +6836,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q192" s="17">
+      <c r="Q192" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="V192" s="26"/>
     </row>
     <row r="193" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L193" s="17" cm="1">
+      <c r="L193" s="33" cm="1">
         <f t="array" ref="L193">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D193)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6867,7 +6867,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q193" s="17">
+      <c r="Q193" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6882,7 +6882,7 @@
       <c r="V193" s="26"/>
     </row>
     <row r="194" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L194" s="17" cm="1">
+      <c r="L194" s="33" cm="1">
         <f t="array" ref="L194">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D194)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6898,7 +6898,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q194" s="17">
+      <c r="Q194" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6913,7 +6913,7 @@
       <c r="V194" s="26"/>
     </row>
     <row r="195" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L195" s="17" cm="1">
+      <c r="L195" s="33" cm="1">
         <f t="array" ref="L195">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D195)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6929,7 +6929,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q195" s="17">
+      <c r="Q195" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6944,7 +6944,7 @@
       <c r="V195" s="26"/>
     </row>
     <row r="196" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L196" s="17" cm="1">
+      <c r="L196" s="33" cm="1">
         <f t="array" ref="L196">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D196)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6960,7 +6960,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q196" s="17">
+      <c r="Q196" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6975,7 +6975,7 @@
       <c r="V196" s="26"/>
     </row>
     <row r="197" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L197" s="17" cm="1">
+      <c r="L197" s="33" cm="1">
         <f t="array" ref="L197">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D197)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -6991,7 +6991,7 @@
         <f t="shared" ref="P197:P252" si="11">H197+M197</f>
         <v>0</v>
       </c>
-      <c r="Q197" s="17">
+      <c r="Q197" s="33">
         <f t="shared" ref="Q197:Q252" si="12">I197+L197</f>
         <v>0</v>
       </c>
@@ -7006,7 +7006,7 @@
       <c r="V197" s="26"/>
     </row>
     <row r="198" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L198" s="17" cm="1">
+      <c r="L198" s="33" cm="1">
         <f t="array" ref="L198">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D198)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7022,7 +7022,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q198" s="17">
+      <c r="Q198" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7037,7 +7037,7 @@
       <c r="V198" s="26"/>
     </row>
     <row r="199" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L199" s="17" cm="1">
+      <c r="L199" s="33" cm="1">
         <f t="array" ref="L199">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D199)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7053,7 +7053,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q199" s="17">
+      <c r="Q199" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7068,7 +7068,7 @@
       <c r="V199" s="26"/>
     </row>
     <row r="200" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L200" s="17" cm="1">
+      <c r="L200" s="33" cm="1">
         <f t="array" ref="L200">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D200)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7084,7 +7084,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q200" s="17">
+      <c r="Q200" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7099,7 +7099,7 @@
       <c r="V200" s="26"/>
     </row>
     <row r="201" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L201" s="17" cm="1">
+      <c r="L201" s="33" cm="1">
         <f t="array" ref="L201">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D201)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7115,7 +7115,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q201" s="17">
+      <c r="Q201" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7130,7 +7130,7 @@
       <c r="V201" s="26"/>
     </row>
     <row r="202" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L202" s="17" cm="1">
+      <c r="L202" s="33" cm="1">
         <f t="array" ref="L202">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D202)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7146,7 +7146,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q202" s="17">
+      <c r="Q202" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7161,7 +7161,7 @@
       <c r="V202" s="26"/>
     </row>
     <row r="203" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L203" s="17" cm="1">
+      <c r="L203" s="33" cm="1">
         <f t="array" ref="L203">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D203)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7177,7 +7177,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q203" s="17">
+      <c r="Q203" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7192,7 +7192,7 @@
       <c r="V203" s="26"/>
     </row>
     <row r="204" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L204" s="17" cm="1">
+      <c r="L204" s="33" cm="1">
         <f t="array" ref="L204">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D204)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7208,7 +7208,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q204" s="17">
+      <c r="Q204" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7223,7 +7223,7 @@
       <c r="V204" s="26"/>
     </row>
     <row r="205" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L205" s="17" cm="1">
+      <c r="L205" s="33" cm="1">
         <f t="array" ref="L205">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D205)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7239,7 +7239,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q205" s="17">
+      <c r="Q205" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7254,7 +7254,7 @@
       <c r="V205" s="26"/>
     </row>
     <row r="206" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L206" s="17" cm="1">
+      <c r="L206" s="33" cm="1">
         <f t="array" ref="L206">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D206)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7270,7 +7270,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q206" s="17">
+      <c r="Q206" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7285,7 +7285,7 @@
       <c r="V206" s="26"/>
     </row>
     <row r="207" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L207" s="17" cm="1">
+      <c r="L207" s="33" cm="1">
         <f t="array" ref="L207">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D207)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7301,7 +7301,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q207" s="17">
+      <c r="Q207" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7316,7 +7316,7 @@
       <c r="V207" s="26"/>
     </row>
     <row r="208" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L208" s="17" cm="1">
+      <c r="L208" s="33" cm="1">
         <f t="array" ref="L208">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D208)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7332,7 +7332,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q208" s="17">
+      <c r="Q208" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7347,7 +7347,7 @@
       <c r="V208" s="26"/>
     </row>
     <row r="209" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L209" s="17" cm="1">
+      <c r="L209" s="33" cm="1">
         <f t="array" ref="L209">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D209)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7363,7 +7363,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q209" s="17">
+      <c r="Q209" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="V209" s="26"/>
     </row>
     <row r="210" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L210" s="17" cm="1">
+      <c r="L210" s="33" cm="1">
         <f t="array" ref="L210">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D210)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7394,7 +7394,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q210" s="17">
+      <c r="Q210" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7409,7 +7409,7 @@
       <c r="V210" s="26"/>
     </row>
     <row r="211" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L211" s="17" cm="1">
+      <c r="L211" s="33" cm="1">
         <f t="array" ref="L211">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D211)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7425,7 +7425,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q211" s="17">
+      <c r="Q211" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="V211" s="26"/>
     </row>
     <row r="212" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L212" s="17" cm="1">
+      <c r="L212" s="33" cm="1">
         <f t="array" ref="L212">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D212)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7456,7 +7456,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q212" s="17">
+      <c r="Q212" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7471,7 +7471,7 @@
       <c r="V212" s="26"/>
     </row>
     <row r="213" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L213" s="17" cm="1">
+      <c r="L213" s="33" cm="1">
         <f t="array" ref="L213">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D213)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7487,7 +7487,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q213" s="17">
+      <c r="Q213" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7502,7 +7502,7 @@
       <c r="V213" s="26"/>
     </row>
     <row r="214" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L214" s="17" cm="1">
+      <c r="L214" s="33" cm="1">
         <f t="array" ref="L214">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D214)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7518,7 +7518,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q214" s="17">
+      <c r="Q214" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7533,7 +7533,7 @@
       <c r="V214" s="26"/>
     </row>
     <row r="215" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L215" s="17" cm="1">
+      <c r="L215" s="33" cm="1">
         <f t="array" ref="L215">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D215)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7549,7 +7549,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q215" s="17">
+      <c r="Q215" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7564,7 +7564,7 @@
       <c r="V215" s="26"/>
     </row>
     <row r="216" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L216" s="17" cm="1">
+      <c r="L216" s="33" cm="1">
         <f t="array" ref="L216">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D216)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7580,7 +7580,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q216" s="17">
+      <c r="Q216" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7595,7 +7595,7 @@
       <c r="V216" s="26"/>
     </row>
     <row r="217" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L217" s="17" cm="1">
+      <c r="L217" s="33" cm="1">
         <f t="array" ref="L217">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D217)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7611,7 +7611,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q217" s="17">
+      <c r="Q217" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7626,7 +7626,7 @@
       <c r="V217" s="26"/>
     </row>
     <row r="218" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L218" s="17" cm="1">
+      <c r="L218" s="33" cm="1">
         <f t="array" ref="L218">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D218)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7642,7 +7642,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q218" s="17">
+      <c r="Q218" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7657,7 +7657,7 @@
       <c r="V218" s="26"/>
     </row>
     <row r="219" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L219" s="17" cm="1">
+      <c r="L219" s="33" cm="1">
         <f t="array" ref="L219">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D219)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7673,7 +7673,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q219" s="17">
+      <c r="Q219" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7688,7 +7688,7 @@
       <c r="V219" s="26"/>
     </row>
     <row r="220" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L220" s="17" cm="1">
+      <c r="L220" s="33" cm="1">
         <f t="array" ref="L220">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D220)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7704,7 +7704,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q220" s="17">
+      <c r="Q220" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7719,7 +7719,7 @@
       <c r="V220" s="26"/>
     </row>
     <row r="221" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L221" s="17" cm="1">
+      <c r="L221" s="33" cm="1">
         <f t="array" ref="L221">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D221)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7735,7 +7735,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q221" s="17">
+      <c r="Q221" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7750,7 +7750,7 @@
       <c r="V221" s="26"/>
     </row>
     <row r="222" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L222" s="17" cm="1">
+      <c r="L222" s="33" cm="1">
         <f t="array" ref="L222">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D222)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7766,7 +7766,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q222" s="17">
+      <c r="Q222" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7781,7 +7781,7 @@
       <c r="V222" s="26"/>
     </row>
     <row r="223" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L223" s="17" cm="1">
+      <c r="L223" s="33" cm="1">
         <f t="array" ref="L223">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D223)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7797,7 +7797,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q223" s="17">
+      <c r="Q223" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7812,7 +7812,7 @@
       <c r="V223" s="26"/>
     </row>
     <row r="224" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L224" s="17" cm="1">
+      <c r="L224" s="33" cm="1">
         <f t="array" ref="L224">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D224)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7828,7 +7828,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q224" s="17">
+      <c r="Q224" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7843,7 +7843,7 @@
       <c r="V224" s="26"/>
     </row>
     <row r="225" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L225" s="17" cm="1">
+      <c r="L225" s="33" cm="1">
         <f t="array" ref="L225">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D225)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7859,7 +7859,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q225" s="17">
+      <c r="Q225" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="V225" s="26"/>
     </row>
     <row r="226" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L226" s="17" cm="1">
+      <c r="L226" s="33" cm="1">
         <f t="array" ref="L226">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D226)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7890,7 +7890,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q226" s="17">
+      <c r="Q226" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7905,7 +7905,7 @@
       <c r="V226" s="26"/>
     </row>
     <row r="227" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L227" s="17" cm="1">
+      <c r="L227" s="33" cm="1">
         <f t="array" ref="L227">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D227)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7921,7 +7921,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q227" s="17">
+      <c r="Q227" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7936,7 +7936,7 @@
       <c r="V227" s="26"/>
     </row>
     <row r="228" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L228" s="17" cm="1">
+      <c r="L228" s="33" cm="1">
         <f t="array" ref="L228">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D228)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7952,7 +7952,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q228" s="17">
+      <c r="Q228" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7967,7 +7967,7 @@
       <c r="V228" s="26"/>
     </row>
     <row r="229" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L229" s="17" cm="1">
+      <c r="L229" s="33" cm="1">
         <f t="array" ref="L229">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D229)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -7983,7 +7983,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q229" s="17">
+      <c r="Q229" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -7998,7 +7998,7 @@
       <c r="V229" s="26"/>
     </row>
     <row r="230" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L230" s="17" cm="1">
+      <c r="L230" s="33" cm="1">
         <f t="array" ref="L230">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D230)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8014,7 +8014,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q230" s="17">
+      <c r="Q230" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8029,7 +8029,7 @@
       <c r="V230" s="26"/>
     </row>
     <row r="231" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L231" s="17" cm="1">
+      <c r="L231" s="33" cm="1">
         <f t="array" ref="L231">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D231)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8045,7 +8045,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q231" s="17">
+      <c r="Q231" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8060,7 +8060,7 @@
       <c r="V231" s="26"/>
     </row>
     <row r="232" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L232" s="17" cm="1">
+      <c r="L232" s="33" cm="1">
         <f t="array" ref="L232">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D232)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8076,7 +8076,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q232" s="17">
+      <c r="Q232" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8091,7 +8091,7 @@
       <c r="V232" s="26"/>
     </row>
     <row r="233" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L233" s="17" cm="1">
+      <c r="L233" s="33" cm="1">
         <f t="array" ref="L233">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D233)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8107,7 +8107,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q233" s="17">
+      <c r="Q233" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8122,7 +8122,7 @@
       <c r="V233" s="26"/>
     </row>
     <row r="234" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L234" s="17" cm="1">
+      <c r="L234" s="33" cm="1">
         <f t="array" ref="L234">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D234)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8138,7 +8138,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q234" s="17">
+      <c r="Q234" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8153,7 +8153,7 @@
       <c r="V234" s="26"/>
     </row>
     <row r="235" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L235" s="17" cm="1">
+      <c r="L235" s="33" cm="1">
         <f t="array" ref="L235">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D235)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8169,7 +8169,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q235" s="17">
+      <c r="Q235" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8184,7 +8184,7 @@
       <c r="V235" s="26"/>
     </row>
     <row r="236" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L236" s="17" cm="1">
+      <c r="L236" s="33" cm="1">
         <f t="array" ref="L236">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D236)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8200,7 +8200,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q236" s="17">
+      <c r="Q236" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8215,7 +8215,7 @@
       <c r="V236" s="26"/>
     </row>
     <row r="237" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L237" s="17" cm="1">
+      <c r="L237" s="33" cm="1">
         <f t="array" ref="L237">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D237)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8231,7 +8231,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q237" s="17">
+      <c r="Q237" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8246,7 +8246,7 @@
       <c r="V237" s="26"/>
     </row>
     <row r="238" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L238" s="17" cm="1">
+      <c r="L238" s="33" cm="1">
         <f t="array" ref="L238">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D238)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8262,7 +8262,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q238" s="17">
+      <c r="Q238" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8277,7 +8277,7 @@
       <c r="V238" s="26"/>
     </row>
     <row r="239" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L239" s="17" cm="1">
+      <c r="L239" s="33" cm="1">
         <f t="array" ref="L239">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D239)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8293,7 +8293,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q239" s="17">
+      <c r="Q239" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8308,7 +8308,7 @@
       <c r="V239" s="26"/>
     </row>
     <row r="240" spans="12:22" x14ac:dyDescent="0.25">
-      <c r="L240" s="17" cm="1">
+      <c r="L240" s="33" cm="1">
         <f t="array" ref="L240">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D240)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8324,7 +8324,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q240" s="17">
+      <c r="Q240" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8339,7 +8339,7 @@
       <c r="V240" s="26"/>
     </row>
     <row r="241" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L241" s="17" cm="1">
+      <c r="L241" s="33" cm="1">
         <f t="array" ref="L241">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D241)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8355,7 +8355,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q241" s="17">
+      <c r="Q241" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8370,7 +8370,7 @@
       <c r="V241" s="26"/>
     </row>
     <row r="242" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L242" s="17" cm="1">
+      <c r="L242" s="33" cm="1">
         <f t="array" ref="L242">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D242)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8386,7 +8386,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q242" s="17">
+      <c r="Q242" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="V242" s="26"/>
     </row>
     <row r="243" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L243" s="17" cm="1">
+      <c r="L243" s="33" cm="1">
         <f t="array" ref="L243">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D243)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8417,7 +8417,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q243" s="17">
+      <c r="Q243" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8432,7 +8432,7 @@
       <c r="V243" s="26"/>
     </row>
     <row r="244" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L244" s="17" cm="1">
+      <c r="L244" s="33" cm="1">
         <f t="array" ref="L244">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D244)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8448,7 +8448,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q244" s="17">
+      <c r="Q244" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8463,7 +8463,7 @@
       <c r="V244" s="26"/>
     </row>
     <row r="245" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L245" s="17" cm="1">
+      <c r="L245" s="33" cm="1">
         <f t="array" ref="L245">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D245)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8479,7 +8479,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q245" s="17">
+      <c r="Q245" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8494,7 +8494,7 @@
       <c r="V245" s="26"/>
     </row>
     <row r="246" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L246" s="17" cm="1">
+      <c r="L246" s="33" cm="1">
         <f t="array" ref="L246">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D246)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8510,7 +8510,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q246" s="17">
+      <c r="Q246" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="V246" s="26"/>
     </row>
     <row r="247" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L247" s="17" cm="1">
+      <c r="L247" s="33" cm="1">
         <f t="array" ref="L247">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D247)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8541,7 +8541,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q247" s="17">
+      <c r="Q247" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8556,7 +8556,7 @@
       <c r="V247" s="26"/>
     </row>
     <row r="248" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L248" s="17" cm="1">
+      <c r="L248" s="33" cm="1">
         <f t="array" ref="L248">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D248)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8572,7 +8572,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q248" s="17">
+      <c r="Q248" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8587,7 +8587,7 @@
       <c r="V248" s="26"/>
     </row>
     <row r="249" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L249" s="17" cm="1">
+      <c r="L249" s="33" cm="1">
         <f t="array" ref="L249">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D249)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8603,7 +8603,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q249" s="17">
+      <c r="Q249" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="V249" s="26"/>
     </row>
     <row r="250" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L250" s="17" cm="1">
+      <c r="L250" s="33" cm="1">
         <f t="array" ref="L250">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D250)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8634,7 +8634,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q250" s="17">
+      <c r="Q250" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8649,7 +8649,7 @@
       <c r="V250" s="26"/>
     </row>
     <row r="251" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L251" s="17" cm="1">
+      <c r="L251" s="33" cm="1">
         <f t="array" ref="L251">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D251)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8665,7 +8665,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q251" s="17">
+      <c r="Q251" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -8680,7 +8680,7 @@
       <c r="V251" s="26"/>
     </row>
     <row r="252" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L252" s="17" cm="1">
+      <c r="L252" s="33" cm="1">
         <f t="array" ref="L252">SUMPRODUCT(('Transaction Glossary'!F$5:F$999=D252)*('Transaction Glossary'!J$5:J$999))</f>
         <v>0</v>
       </c>
@@ -8696,7 +8696,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q252" s="17">
+      <c r="Q252" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v/>
       </c>
       <c r="M6" s="17" t="str">
-        <f>IF(J6="", "",IF(E6="Buy", L5*M5+(-K6)/L6, M5))</f>
+        <f>IF(J6="", "",IF(E6="Buy", (L5*M5+(-K6))/L6, M5))</f>
         <v/>
       </c>
       <c r="N6" s="17" t="str">
@@ -9160,7 +9160,7 @@
         <v/>
       </c>
       <c r="M7" s="17" t="str">
-        <f t="shared" ref="M7:M70" si="1">IF(J7="", "",IF(E7="Buy", L6*M6+(-K7)/L7, M6))</f>
+        <f t="shared" ref="M7:M70" si="1">IF(J7="", "",IF(E7="Buy", (L6*M6+(-K7))/L7, M6))</f>
         <v/>
       </c>
       <c r="N7" s="17" t="str">
@@ -10506,7 +10506,7 @@
         <v/>
       </c>
       <c r="M71" s="17" t="str">
-        <f t="shared" ref="M71:M134" si="5">IF(J71="", "",IF(E71="Buy", L70*M70+(-K71)/L71, M70))</f>
+        <f t="shared" ref="M71:M134" si="5">IF(J71="", "",IF(E71="Buy", (L70*M70+(-K71))/L71, M70))</f>
         <v/>
       </c>
       <c r="N71" s="17" t="str">
@@ -11850,7 +11850,7 @@
         <v/>
       </c>
       <c r="M135" s="17" t="str">
-        <f t="shared" ref="M135:M154" si="9">IF(J135="", "",IF(E135="Buy", L134*M134+(-K135)/L135, M134))</f>
+        <f t="shared" ref="M135:M198" si="9">IF(J135="", "",IF(E135="Buy", (L134*M134+(-K135))/L135, M134))</f>
         <v/>
       </c>
       <c r="N135" s="17" t="str">
@@ -12276,15 +12276,15 @@
         <v/>
       </c>
       <c r="M155" s="17" t="str">
-        <f t="shared" ref="M155:M218" si="13">IF(J155="", "",IF(E155="Buy", L154*M154+(-K155)/L155, M154))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N155" s="17" t="str">
-        <f t="shared" ref="N155:N218" si="14">IF(J155="", "", IF(E155="Sell",K155, 0))</f>
+        <f t="shared" ref="N155:N218" si="13">IF(J155="", "", IF(E155="Sell",K155, 0))</f>
         <v/>
       </c>
       <c r="O155" s="17" t="str">
-        <f t="shared" ref="O155:O218" si="15">IF(J155="", "", IF(E155="Sell", N155+J155*M155, 0))</f>
+        <f t="shared" ref="O155:O218" si="14">IF(J155="", "", IF(E155="Sell", N155+J155*M155, 0))</f>
         <v/>
       </c>
       <c r="P155" s="17"/>
@@ -12295,15 +12295,15 @@
         <v/>
       </c>
       <c r="M156" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N156" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O156" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12313,15 +12313,15 @@
         <v/>
       </c>
       <c r="M157" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N157" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N157" t="str">
+      <c r="O157" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O157" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12331,15 +12331,15 @@
         <v/>
       </c>
       <c r="M158" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N158" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N158" t="str">
+      <c r="O158" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O158" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12349,15 +12349,15 @@
         <v/>
       </c>
       <c r="M159" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N159" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N159" t="str">
+      <c r="O159" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O159" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12367,15 +12367,15 @@
         <v/>
       </c>
       <c r="M160" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N160" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N160" t="str">
+      <c r="O160" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O160" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12385,15 +12385,15 @@
         <v/>
       </c>
       <c r="M161" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N161" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N161" t="str">
+      <c r="O161" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O161" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12403,15 +12403,15 @@
         <v/>
       </c>
       <c r="M162" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N162" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N162" t="str">
+      <c r="O162" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O162" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12421,15 +12421,15 @@
         <v/>
       </c>
       <c r="M163" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N163" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N163" t="str">
+      <c r="O163" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O163" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12439,15 +12439,15 @@
         <v/>
       </c>
       <c r="M164" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N164" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N164" t="str">
+      <c r="O164" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O164" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12457,15 +12457,15 @@
         <v/>
       </c>
       <c r="M165" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N165" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N165" t="str">
+      <c r="O165" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O165" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12475,15 +12475,15 @@
         <v/>
       </c>
       <c r="M166" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N166" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N166" t="str">
+      <c r="O166" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O166" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12493,15 +12493,15 @@
         <v/>
       </c>
       <c r="M167" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N167" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N167" t="str">
+      <c r="O167" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O167" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12511,15 +12511,15 @@
         <v/>
       </c>
       <c r="M168" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N168" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N168" t="str">
+      <c r="O168" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O168" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12529,15 +12529,15 @@
         <v/>
       </c>
       <c r="M169" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N169" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N169" t="str">
+      <c r="O169" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O169" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12547,15 +12547,15 @@
         <v/>
       </c>
       <c r="M170" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N170" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N170" t="str">
+      <c r="O170" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O170" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12565,15 +12565,15 @@
         <v/>
       </c>
       <c r="M171" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N171" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N171" t="str">
+      <c r="O171" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O171" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12583,15 +12583,15 @@
         <v/>
       </c>
       <c r="M172" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N172" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N172" t="str">
+      <c r="O172" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O172" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12601,15 +12601,15 @@
         <v/>
       </c>
       <c r="M173" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N173" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N173" t="str">
+      <c r="O173" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O173" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12619,15 +12619,15 @@
         <v/>
       </c>
       <c r="M174" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N174" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N174" t="str">
+      <c r="O174" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O174" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12637,15 +12637,15 @@
         <v/>
       </c>
       <c r="M175" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N175" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N175" t="str">
+      <c r="O175" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O175" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12655,15 +12655,15 @@
         <v/>
       </c>
       <c r="M176" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N176" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N176" t="str">
+      <c r="O176" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O176" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12673,15 +12673,15 @@
         <v/>
       </c>
       <c r="M177" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N177" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N177" t="str">
+      <c r="O177" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O177" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12691,15 +12691,15 @@
         <v/>
       </c>
       <c r="M178" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N178" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N178" t="str">
+      <c r="O178" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O178" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12709,15 +12709,15 @@
         <v/>
       </c>
       <c r="M179" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N179" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N179" t="str">
+      <c r="O179" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O179" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12727,15 +12727,15 @@
         <v/>
       </c>
       <c r="M180" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N180" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N180" t="str">
+      <c r="O180" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O180" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12745,15 +12745,15 @@
         <v/>
       </c>
       <c r="M181" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N181" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N181" t="str">
+      <c r="O181" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O181" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12763,15 +12763,15 @@
         <v/>
       </c>
       <c r="M182" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N182" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N182" t="str">
+      <c r="O182" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O182" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12781,15 +12781,15 @@
         <v/>
       </c>
       <c r="M183" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N183" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N183" t="str">
+      <c r="O183" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O183" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12799,15 +12799,15 @@
         <v/>
       </c>
       <c r="M184" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N184" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N184" t="str">
+      <c r="O184" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O184" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12817,15 +12817,15 @@
         <v/>
       </c>
       <c r="M185" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N185" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N185" t="str">
+      <c r="O185" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O185" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12835,15 +12835,15 @@
         <v/>
       </c>
       <c r="M186" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N186" t="str">
+      <c r="O186" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O186" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12853,15 +12853,15 @@
         <v/>
       </c>
       <c r="M187" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N187" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N187" t="str">
+      <c r="O187" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O187" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12871,15 +12871,15 @@
         <v/>
       </c>
       <c r="M188" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N188" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N188" t="str">
+      <c r="O188" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O188" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12889,15 +12889,15 @@
         <v/>
       </c>
       <c r="M189" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N189" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N189" t="str">
+      <c r="O189" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O189" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12907,15 +12907,15 @@
         <v/>
       </c>
       <c r="M190" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N190" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N190" t="str">
+      <c r="O190" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O190" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12925,15 +12925,15 @@
         <v/>
       </c>
       <c r="M191" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N191" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N191" t="str">
+      <c r="O191" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O191" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12943,15 +12943,15 @@
         <v/>
       </c>
       <c r="M192" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N192" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N192" t="str">
+      <c r="O192" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O192" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12961,15 +12961,15 @@
         <v/>
       </c>
       <c r="M193" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N193" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N193" t="str">
+      <c r="O193" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O193" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12979,15 +12979,15 @@
         <v/>
       </c>
       <c r="M194" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N194" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N194" t="str">
+      <c r="O194" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O194" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12997,15 +12997,15 @@
         <v/>
       </c>
       <c r="M195" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N195" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N195" t="str">
+      <c r="O195" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O195" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13015,15 +13015,15 @@
         <v/>
       </c>
       <c r="M196" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N196" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N196" t="str">
+      <c r="O196" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O196" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13033,15 +13033,15 @@
         <v/>
       </c>
       <c r="M197" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N197" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N197" t="str">
+      <c r="O197" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O197" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13051,15 +13051,15 @@
         <v/>
       </c>
       <c r="M198" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="N198" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N198" t="str">
+      <c r="O198" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O198" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13069,15 +13069,15 @@
         <v/>
       </c>
       <c r="M199" t="str">
+        <f t="shared" ref="M199:M253" si="15">IF(J199="", "",IF(E199="Buy", (L198*M198+(-K199))/L199, M198))</f>
+        <v/>
+      </c>
+      <c r="N199" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N199" t="str">
+      <c r="O199" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O199" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13087,15 +13087,15 @@
         <v/>
       </c>
       <c r="M200" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N200" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N200" t="str">
+      <c r="O200" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O200" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13105,15 +13105,15 @@
         <v/>
       </c>
       <c r="M201" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N201" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N201" t="str">
+      <c r="O201" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O201" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13123,15 +13123,15 @@
         <v/>
       </c>
       <c r="M202" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N202" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N202" t="str">
+      <c r="O202" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O202" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13141,15 +13141,15 @@
         <v/>
       </c>
       <c r="M203" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N203" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N203" t="str">
+      <c r="O203" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O203" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13159,15 +13159,15 @@
         <v/>
       </c>
       <c r="M204" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N204" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N204" t="str">
+      <c r="O204" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O204" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13177,15 +13177,15 @@
         <v/>
       </c>
       <c r="M205" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N205" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N205" t="str">
+      <c r="O205" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O205" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13195,15 +13195,15 @@
         <v/>
       </c>
       <c r="M206" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N206" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N206" t="str">
+      <c r="O206" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O206" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13213,15 +13213,15 @@
         <v/>
       </c>
       <c r="M207" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N207" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N207" t="str">
+      <c r="O207" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O207" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13231,15 +13231,15 @@
         <v/>
       </c>
       <c r="M208" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N208" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N208" t="str">
+      <c r="O208" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O208" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13249,15 +13249,15 @@
         <v/>
       </c>
       <c r="M209" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N209" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N209" t="str">
+      <c r="O209" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O209" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13267,15 +13267,15 @@
         <v/>
       </c>
       <c r="M210" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N210" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N210" t="str">
+      <c r="O210" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O210" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13285,15 +13285,15 @@
         <v/>
       </c>
       <c r="M211" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N211" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N211" t="str">
+      <c r="O211" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O211" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13303,15 +13303,15 @@
         <v/>
       </c>
       <c r="M212" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N212" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N212" t="str">
+      <c r="O212" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O212" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13321,15 +13321,15 @@
         <v/>
       </c>
       <c r="M213" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N213" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N213" t="str">
+      <c r="O213" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O213" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13339,15 +13339,15 @@
         <v/>
       </c>
       <c r="M214" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N214" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N214" t="str">
+      <c r="O214" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O214" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13357,15 +13357,15 @@
         <v/>
       </c>
       <c r="M215" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N215" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N215" t="str">
+      <c r="O215" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O215" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13375,15 +13375,15 @@
         <v/>
       </c>
       <c r="M216" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N216" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N216" t="str">
+      <c r="O216" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O216" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13393,15 +13393,15 @@
         <v/>
       </c>
       <c r="M217" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N217" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N217" t="str">
+      <c r="O217" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O217" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13411,15 +13411,15 @@
         <v/>
       </c>
       <c r="M218" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N218" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N218" t="str">
+      <c r="O218" t="str">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O218" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -13429,15 +13429,15 @@
         <v/>
       </c>
       <c r="M219" t="str">
-        <f t="shared" ref="M219:M253" si="17">IF(J219="", "",IF(E219="Buy", L218*M218+(-K219)/L219, M218))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N219" t="str">
-        <f t="shared" ref="N219:N253" si="18">IF(J219="", "", IF(E219="Sell",K219, 0))</f>
+        <f t="shared" ref="N219:N253" si="17">IF(J219="", "", IF(E219="Sell",K219, 0))</f>
         <v/>
       </c>
       <c r="O219" t="str">
-        <f t="shared" ref="O219:O253" si="19">IF(J219="", "", IF(E219="Sell", N219+J219*M219, 0))</f>
+        <f t="shared" ref="O219:O253" si="18">IF(J219="", "", IF(E219="Sell", N219+J219*M219, 0))</f>
         <v/>
       </c>
     </row>
@@ -13447,15 +13447,15 @@
         <v/>
       </c>
       <c r="M220" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N220" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N220" t="str">
+      <c r="O220" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O220" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13465,15 +13465,15 @@
         <v/>
       </c>
       <c r="M221" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N221" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N221" t="str">
+      <c r="O221" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O221" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13483,15 +13483,15 @@
         <v/>
       </c>
       <c r="M222" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N222" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N222" t="str">
+      <c r="O222" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O222" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13501,15 +13501,15 @@
         <v/>
       </c>
       <c r="M223" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N223" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N223" t="str">
+      <c r="O223" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O223" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13519,15 +13519,15 @@
         <v/>
       </c>
       <c r="M224" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N224" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N224" t="str">
+      <c r="O224" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O224" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13537,15 +13537,15 @@
         <v/>
       </c>
       <c r="M225" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N225" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N225" t="str">
+      <c r="O225" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O225" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13555,15 +13555,15 @@
         <v/>
       </c>
       <c r="M226" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N226" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N226" t="str">
+      <c r="O226" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O226" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13573,15 +13573,15 @@
         <v/>
       </c>
       <c r="M227" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N227" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N227" t="str">
+      <c r="O227" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O227" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13591,15 +13591,15 @@
         <v/>
       </c>
       <c r="M228" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N228" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N228" t="str">
+      <c r="O228" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O228" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13609,15 +13609,15 @@
         <v/>
       </c>
       <c r="M229" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N229" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N229" t="str">
+      <c r="O229" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O229" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13627,15 +13627,15 @@
         <v/>
       </c>
       <c r="M230" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N230" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N230" t="str">
+      <c r="O230" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O230" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13645,15 +13645,15 @@
         <v/>
       </c>
       <c r="M231" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N231" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N231" t="str">
+      <c r="O231" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O231" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13663,15 +13663,15 @@
         <v/>
       </c>
       <c r="M232" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N232" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N232" t="str">
+      <c r="O232" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O232" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13681,15 +13681,15 @@
         <v/>
       </c>
       <c r="M233" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N233" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N233" t="str">
+      <c r="O233" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O233" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13699,15 +13699,15 @@
         <v/>
       </c>
       <c r="M234" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N234" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N234" t="str">
+      <c r="O234" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O234" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13717,15 +13717,15 @@
         <v/>
       </c>
       <c r="M235" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N235" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N235" t="str">
+      <c r="O235" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O235" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13735,15 +13735,15 @@
         <v/>
       </c>
       <c r="M236" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N236" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N236" t="str">
+      <c r="O236" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O236" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13753,15 +13753,15 @@
         <v/>
       </c>
       <c r="M237" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N237" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N237" t="str">
+      <c r="O237" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O237" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13771,15 +13771,15 @@
         <v/>
       </c>
       <c r="M238" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N238" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N238" t="str">
+      <c r="O238" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O238" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13789,15 +13789,15 @@
         <v/>
       </c>
       <c r="M239" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N239" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N239" t="str">
+      <c r="O239" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O239" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13807,15 +13807,15 @@
         <v/>
       </c>
       <c r="M240" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N240" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N240" t="str">
+      <c r="O240" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O240" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13825,15 +13825,15 @@
         <v/>
       </c>
       <c r="M241" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N241" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N241" t="str">
+      <c r="O241" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O241" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13843,15 +13843,15 @@
         <v/>
       </c>
       <c r="M242" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N242" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N242" t="str">
+      <c r="O242" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O242" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13861,15 +13861,15 @@
         <v/>
       </c>
       <c r="M243" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N243" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N243" t="str">
+      <c r="O243" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O243" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13879,15 +13879,15 @@
         <v/>
       </c>
       <c r="M244" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N244" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N244" t="str">
+      <c r="O244" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O244" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13897,15 +13897,15 @@
         <v/>
       </c>
       <c r="M245" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N245" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N245" t="str">
+      <c r="O245" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O245" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13915,15 +13915,15 @@
         <v/>
       </c>
       <c r="M246" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N246" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N246" t="str">
+      <c r="O246" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O246" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13933,15 +13933,15 @@
         <v/>
       </c>
       <c r="M247" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N247" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N247" t="str">
+      <c r="O247" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O247" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13951,15 +13951,15 @@
         <v/>
       </c>
       <c r="M248" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N248" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N248" t="str">
+      <c r="O248" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O248" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13969,15 +13969,15 @@
         <v/>
       </c>
       <c r="M249" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N249" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N249" t="str">
+      <c r="O249" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O249" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -13987,15 +13987,15 @@
         <v/>
       </c>
       <c r="M250" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N250" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N250" t="str">
+      <c r="O250" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O250" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14005,15 +14005,15 @@
         <v/>
       </c>
       <c r="M251" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N251" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N251" t="str">
+      <c r="O251" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O251" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14023,15 +14023,15 @@
         <v/>
       </c>
       <c r="M252" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N252" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N252" t="str">
+      <c r="O252" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O252" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14041,15 +14041,15 @@
         <v/>
       </c>
       <c r="M253" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N253" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="N253" t="str">
+      <c r="O253" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O253" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>

--- a/Investment Tracking V3.xlsx
+++ b/Investment Tracking V3.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4750" documentId="8_{B2161804-0EDF-42E0-BE0F-33C496CCEE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{762058FA-5E21-48B6-ADD6-49897A9C74E4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D310D58-D25C-478B-96CD-BDDADD687EF5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5D310D58-D25C-478B-96CD-BDDADD687EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -400,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -466,17 +466,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -493,10 +490,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -839,40 +832,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:28" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="H2" s="43" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="H2" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
       <c r="L2" s="38"/>
       <c r="M2" s="38" t="s">
         <v>44</v>
       </c>
       <c r="N2" s="38"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="43" t="s">
+      <c r="P2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="44" t="s">
+      <c r="X2" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
     </row>
     <row r="3" spans="3:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C3" s="14" t="s">
@@ -973,12 +966,12 @@
       <c r="X4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="48">
+      <c r="Y4" s="43">
         <f>SUM(U4:U252)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48">
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="43">
         <f>Y4-Z4</f>
         <v>0</v>
       </c>
@@ -1020,12 +1013,12 @@
       <c r="X5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Y5" s="48">
+      <c r="Y5" s="43">
         <f>Y4</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48">
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43">
         <f>Y5-Z5</f>
         <v>0</v>
       </c>
@@ -1067,15 +1060,15 @@
       <c r="X6" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="Y6" s="49">
+      <c r="Y6" s="44">
         <f>Y5+Y4</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="49">
+      <c r="Z6" s="44">
         <f t="shared" ref="Z6:AA6" si="4">Z5+Z4</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="49">
+      <c r="AA6" s="44">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -8816,7 +8809,7 @@
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" customWidth="1"/>
     <col min="7" max="7" width="52.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11" style="47" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="11" width="16.140625" customWidth="1"/>
     <col min="12" max="12" width="16.140625" style="19" customWidth="1"/>
     <col min="13" max="13" width="16.140625" customWidth="1"/>
@@ -8841,7 +8834,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="45"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -8875,7 +8868,7 @@
       <c r="G4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="14" t="s">
         <v>26</v>
       </c>
       <c r="I4" s="15" t="s">
@@ -8959,7 +8952,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="45"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
